--- a/excel/pardadex_capacitaciones.xlsx
+++ b/excel/pardadex_capacitaciones.xlsx
@@ -598,12 +598,12 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>C001165739</t>
+          <t>C001078661</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>C001165739 - DIAZ SILVA EDELMIRA</t>
+          <t>C001078661 - TIMANA BECERRA NANCI</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -631,7 +631,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -692,12 +692,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>C001078661</t>
+          <t>C001078670</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>C001078661 - TIMANA BECERRA NANCI</t>
+          <t>C001078670 - GONZALES GONZALES MARIA FRANCISCA</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -723,11 +723,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
@@ -786,12 +782,12 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>C001078670</t>
+          <t>C001082584</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>C001078670 - GONZALES GONZALES MARIA FRANCISCA</t>
+          <t>C001082584 - VASQUEZ CADENILLAS LUZMILA</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -876,12 +872,12 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>C001082584</t>
+          <t>C001084161</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>C001082584 - VASQUEZ CADENILLAS LUZMILA</t>
+          <t>C001084161 - ARRASCUE MUÑOZ ARIACELI</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -907,7 +903,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
@@ -966,12 +966,12 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>C001084161</t>
+          <t>C001165739</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>C001084161 - ARRASCUE MUÑOZ ARIACELI</t>
+          <t>C001165739 - DIAZ SILVA EDELMIRA</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -999,7 +999,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>1000009104</t>
+          <t>1000049464</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1060,12 +1060,12 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>C001378688</t>
+          <t>C001361114</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>C001378688 - OLIVERA PIEDRA MARIA NELIDA</t>
+          <t>C001361114 - BARBOZA DE ACUÑA MARIA VIDALA</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>C001378988</t>
+          <t>C001403645</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>C001378988 - MORI CAPITAN TERESA</t>
+          <t>C001403645 - SILVA TARRILLO MIRIAM ZOILA</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1248,12 +1248,12 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>C001361114</t>
+          <t>C001402282</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>C001361114 - BARBOZA DE ACUÑA MARIA VIDALA</t>
+          <t>C001402282 - MATEO MORETO CLORINDA</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1322,7 +1322,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>1000049464</t>
+          <t>1000009104</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1342,12 +1342,12 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>C001402282</t>
+          <t>C001378688</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>C001402282 - MATEO MORETO CLORINDA</t>
+          <t>C001378688 - OLIVERA PIEDRA MARIA NELIDA</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1436,12 +1436,12 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>C001403645</t>
+          <t>C001378988</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>C001403645 - SILVA TARRILLO MIRIAM ZOILA</t>
+          <t>C001378988 - MORI CAPITAN TERESA</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1469,7 +1469,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -1530,12 +1530,12 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>C001518360</t>
+          <t>C001696242</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>C001518360 - GONZALEZ GONZALEZ MARIA JUANA</t>
+          <t>C001696242 - MARCHENA GONZA NELIDA</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1563,7 +1563,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -1614,7 +1614,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>No tiene tiempo para capacitarse</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1624,17 +1624,17 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>C001518368</t>
+          <t>C001620145</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>C001518368 - MIRANDA ARRASCUE MARIA ELIZABETH</t>
+          <t>C001620145 - LEYVA ROBLES ERIC YOEL</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="I13" s="2" t="n">
@@ -1647,7 +1647,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1662,21 +1662,9 @@
       </c>
       <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr"/>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="Q13" t="inlineStr">
-        <is>
-          <t>Ninguna, entendió correctamente</t>
-        </is>
-      </c>
-      <c r="R13" t="inlineStr">
-        <is>
-          <t>Mejores promociones</t>
-        </is>
-      </c>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="inlineStr"/>
       <c r="S13" t="inlineStr"/>
       <c r="T13" t="inlineStr">
         <is>
@@ -1708,7 +1696,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>No tiene tiempo para capacitarse</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1718,17 +1706,17 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>C001620145</t>
+          <t>C001518360</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>C001620145 - LEYVA ROBLES ERIC YOEL</t>
+          <t>C001518360 - GONZALEZ GONZALEZ MARIA JUANA</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="I14" s="2" t="n">
@@ -1741,7 +1729,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1751,14 +1739,26 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr"/>
-      <c r="P14" t="inlineStr"/>
-      <c r="Q14" t="inlineStr"/>
-      <c r="R14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>Ninguna, entendió correctamente</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
       <c r="S14" t="inlineStr"/>
       <c r="T14" t="inlineStr">
         <is>
@@ -1800,12 +1800,12 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>C001541837</t>
+          <t>C001518368</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>C001541837 - DELGADO DE OJEDA ESPERANZA</t>
+          <t>C001518368 - MIRANDA ARRASCUE MARIA ELIZABETH</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
@@ -1984,12 +1984,12 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>C004097806</t>
+          <t>C001541837</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>C004097806 - HERNANDEZ FLORES WILDOR</t>
+          <t>C001541837 - DELGADO DE OJEDA ESPERANZA</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2015,7 +2015,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
       <c r="N17" t="inlineStr"/>
       <c r="O17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
@@ -2164,12 +2168,12 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>C001733892</t>
+          <t>C004097806</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>C001733892 - LEYVA MELENDEZ JORGE LUIS</t>
+          <t>C004097806 - HERNANDEZ FLORES WILDOR</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2254,12 +2258,12 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>C001726026</t>
+          <t>C001733892</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>C001726026 - CHAVEZ CHAVEZ MARISOL</t>
+          <t>C001733892 - LEYVA MELENDEZ JORGE LUIS</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2285,11 +2289,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
+      <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="O20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
@@ -2348,12 +2348,12 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>C001696242</t>
+          <t>C001726026</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>C001696242 - MARCHENA GONZA NELIDA</t>
+          <t>C001726026 - CHAVEZ CHAVEZ MARISOL</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2381,7 +2381,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="N21" t="inlineStr"/>
@@ -2442,12 +2442,12 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>C001654507</t>
+          <t>C001076401</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>C001654507 - CHAPOÑAN CHAPOÑAN MARIA ISABEL</t>
+          <t>C001076401 - DELGADO RUIZ FILOMENA MADY</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>C001645928</t>
+          <t>C001704763</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>C001645928 - QUIROZ SARABIA HENRRY YHOMNE</t>
+          <t>C001704763 - CORONEL CERCADO JEINER</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2630,12 +2630,12 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>C001620923</t>
+          <t>C001711174</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>C001620923 - FERNANDEZ HERNANDEZ ERICK IGOR</t>
+          <t>C001711174 - ACUÑA MEJIA CARMELA</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -2661,11 +2661,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
+      <c r="M24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="O24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
@@ -2714,7 +2710,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>No tiene tiempo para capacitarse</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -2724,17 +2720,17 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>C001570557</t>
+          <t>C001620923</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>C001570557 - SANTISTEBAN ACOSTA SEBASTIAN</t>
+          <t>C001620923 - FERNANDEZ HERNANDEZ ERICK IGOR</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="I25" s="2" t="n">
@@ -2747,7 +2743,7 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -2762,9 +2758,21 @@
       </c>
       <c r="N25" t="inlineStr"/>
       <c r="O25" t="inlineStr"/>
-      <c r="P25" t="inlineStr"/>
-      <c r="Q25" t="inlineStr"/>
-      <c r="R25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>Ninguna, entendió correctamente</t>
+        </is>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
       <c r="S25" t="inlineStr"/>
       <c r="T25" t="inlineStr">
         <is>
@@ -2806,12 +2814,12 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>C004165835</t>
+          <t>C001645928</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>C004165835 - AREVALO PEREZ MARIA NELLY</t>
+          <t>C001645928 - QUIROZ SARABIA HENRRY YHOMNE</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2837,7 +2845,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
       <c r="N26" t="inlineStr"/>
       <c r="O26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
@@ -2896,12 +2908,12 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>C004069881</t>
+          <t>C001654507</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>C004069881 - GIL HOYOS GLORIA LUZ</t>
+          <t>C001654507 - CHAPOÑAN CHAPOÑAN MARIA ISABEL</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2980,7 +2992,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>No tiene tiempo para capacitarse</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -2990,17 +3002,17 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>C001704763</t>
+          <t>C001570557</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>C001704763 - CORONEL CERCADO JEINER</t>
+          <t>C001570557 - SANTISTEBAN ACOSTA SEBASTIAN</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="I28" s="2" t="n">
@@ -3013,7 +3025,7 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -3023,26 +3035,14 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="N28" t="inlineStr"/>
       <c r="O28" t="inlineStr"/>
-      <c r="P28" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="Q28" t="inlineStr">
-        <is>
-          <t>Ninguna, entendió correctamente</t>
-        </is>
-      </c>
-      <c r="R28" t="inlineStr">
-        <is>
-          <t>Mejores promociones</t>
-        </is>
-      </c>
+      <c r="P28" t="inlineStr"/>
+      <c r="Q28" t="inlineStr"/>
+      <c r="R28" t="inlineStr"/>
       <c r="S28" t="inlineStr"/>
       <c r="T28" t="inlineStr">
         <is>
@@ -3084,12 +3084,12 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>C001711174</t>
+          <t>C004069881</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>C001711174 - ACUÑA MEJIA CARMELA</t>
+          <t>C004069881 - GIL HOYOS GLORIA LUZ</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -3115,7 +3115,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
       <c r="N29" t="inlineStr"/>
       <c r="O29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
@@ -3174,12 +3178,12 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>C001715659</t>
+          <t>C001753329</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>C001715659 - RAMIREZ BARBOZA LIBORIO</t>
+          <t>C001753329 - VILLALOBOS PEREZ DEISY</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -3207,7 +3211,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="N30" t="inlineStr"/>
@@ -3268,12 +3272,12 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>C001726771</t>
+          <t>C001747786</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>C001726771 - ARTEAGA GIL GIANELLA BRIGITTE</t>
+          <t>C001747786 - SILVA ALVARADO ERESBITA ARACELI</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -3299,7 +3303,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
       <c r="N31" t="inlineStr"/>
       <c r="O31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
@@ -3452,12 +3460,12 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>C001747786</t>
+          <t>C001726771</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>C001747786 - SILVA ALVARADO ERESBITA ARACELI</t>
+          <t>C001726771 - ARTEAGA GIL GIANELLA BRIGITTE</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -3483,11 +3491,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
+      <c r="M33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
       <c r="O33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
@@ -3546,12 +3550,12 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>C001753329</t>
+          <t>C001715659</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>C001753329 - VILLALOBOS PEREZ DEISY</t>
+          <t>C001715659 - RAMIREZ BARBOZA LIBORIO</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -3579,7 +3583,7 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="N34" t="inlineStr"/>
@@ -3640,12 +3644,12 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>C001076401</t>
+          <t>C004165835</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>C001076401 - DELGADO RUIZ FILOMENA MADY</t>
+          <t>C004165835 - AREVALO PEREZ MARIA NELLY</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -3671,11 +3675,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
+      <c r="M35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
       <c r="O35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
@@ -3734,12 +3734,12 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>C004240567</t>
+          <t>C001507751</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>C004240567 - DIAZ MEDINA MARIA NELLY</t>
+          <t>C001507751 - MANAY SALAZAR MARIA DEL CARMEN</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -3804,7 +3804,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>1000009104</t>
+          <t>1000049464</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -3814,7 +3814,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>No tiene tiempo para capacitarse</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -3824,17 +3824,17 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>C001377892</t>
+          <t>C001550336</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>C001377892 - CUBAS SANCHEZ SILVIA JANET</t>
+          <t>C001550336 - RODAS SANCHEZ CARMEN MERLY</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="I37" s="2" t="n">
@@ -3847,7 +3847,7 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -3858,9 +3858,21 @@
       <c r="M37" t="inlineStr"/>
       <c r="N37" t="inlineStr"/>
       <c r="O37" t="inlineStr"/>
-      <c r="P37" t="inlineStr"/>
-      <c r="Q37" t="inlineStr"/>
-      <c r="R37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>Ninguna, entendió correctamente</t>
+        </is>
+      </c>
+      <c r="R37" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
       <c r="S37" t="inlineStr"/>
       <c r="T37" t="inlineStr">
         <is>
@@ -3892,7 +3904,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>No tiene tiempo para capacitarse</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -3902,17 +3914,17 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>C001549310</t>
+          <t>C001377892</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>C001549310 - BENAVIDES SAAVEDRA MARITA GUISELA</t>
+          <t>C001377892 - CUBAS SANCHEZ SILVIA JANET</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="I38" s="2" t="n">
@@ -3925,7 +3937,7 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -3936,21 +3948,9 @@
       <c r="M38" t="inlineStr"/>
       <c r="N38" t="inlineStr"/>
       <c r="O38" t="inlineStr"/>
-      <c r="P38" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="Q38" t="inlineStr">
-        <is>
-          <t>Ninguna, entendió correctamente</t>
-        </is>
-      </c>
-      <c r="R38" t="inlineStr">
-        <is>
-          <t>Mejores promociones</t>
-        </is>
-      </c>
+      <c r="P38" t="inlineStr"/>
+      <c r="Q38" t="inlineStr"/>
+      <c r="R38" t="inlineStr"/>
       <c r="S38" t="inlineStr"/>
       <c r="T38" t="inlineStr">
         <is>
@@ -3992,12 +3992,12 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>C001691214</t>
+          <t>C001078756</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>C001691214 - SANCHEZ TEJADA DORIS</t>
+          <t>C001078756 - TARRILLO MEJIA ALEX JAVIER</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -4076,7 +4076,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>No tiene tiempo para capacitarse</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -4086,17 +4086,17 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>C001707748</t>
+          <t>C001549310</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>C001707748 - ESTELA GAMARRA PERCY</t>
+          <t>C001549310 - BENAVIDES SAAVEDRA MARITA GUISELA</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="I40" s="2" t="n">
@@ -4109,7 +4109,7 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -4120,9 +4120,21 @@
       <c r="M40" t="inlineStr"/>
       <c r="N40" t="inlineStr"/>
       <c r="O40" t="inlineStr"/>
-      <c r="P40" t="inlineStr"/>
-      <c r="Q40" t="inlineStr"/>
-      <c r="R40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>Ninguna, entendió correctamente</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
       <c r="S40" t="inlineStr"/>
       <c r="T40" t="inlineStr">
         <is>
@@ -4144,7 +4156,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>1000049464</t>
+          <t>1000009104</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -4154,7 +4166,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>No tiene tiempo para capacitarse</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -4164,17 +4176,17 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>C004047923</t>
+          <t>C004240567</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>C004047923 - HERRERA BALLENA JACKELINE DEL PILAR</t>
+          <t>C004240567 - DIAZ MEDINA MARIA NELLY</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="I41" s="2" t="n">
@@ -4187,7 +4199,7 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -4195,16 +4207,24 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
+      <c r="M41" t="inlineStr"/>
       <c r="N41" t="inlineStr"/>
       <c r="O41" t="inlineStr"/>
-      <c r="P41" t="inlineStr"/>
-      <c r="Q41" t="inlineStr"/>
-      <c r="R41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>Ninguna, entendió correctamente</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
       <c r="S41" t="inlineStr"/>
       <c r="T41" t="inlineStr">
         <is>
@@ -4246,12 +4266,12 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>C004160544</t>
+          <t>C001733353</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>C004160544 - SALAZAR DE GONZALES PAULITA</t>
+          <t>C001733353 - CARRERO GUTIERREZ YEISER ESTEFANIA</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -4279,7 +4299,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="N42" t="inlineStr"/>
@@ -4340,12 +4360,12 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>C001656801</t>
+          <t>C004222016</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>C001656801 - ZULOETA ZULOETA HENRY</t>
+          <t>C004222016 - MEJIA MESTANZA SHAROL LICETH</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -4371,7 +4391,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
       <c r="N43" t="inlineStr"/>
       <c r="O43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
@@ -4430,12 +4454,12 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>C001078756</t>
+          <t>C004160544</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>C001078756 - TARRILLO MEJIA ALEX JAVIER</t>
+          <t>C004160544 - SALAZAR DE GONZALES PAULITA</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -4463,7 +4487,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="N44" t="inlineStr"/>
@@ -4524,12 +4548,12 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>C001550336</t>
+          <t>C004161330</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>C001550336 - RODAS SANCHEZ CARMEN MERLY</t>
+          <t>C004161330 - FERNANDEZ ARCELA MILITZA JERSSUNNY</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -4594,7 +4618,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>1000009104</t>
+          <t>1000049464</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -4614,12 +4638,12 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>C001507751</t>
+          <t>C004172442</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>C001507751 - MANAY SALAZAR MARIA DEL CARMEN</t>
+          <t>C004172442 - CORPORACION E INVERSIONES GADIEL E.I.R.L</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -4694,7 +4718,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>No tiene tiempo para capacitarse</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -4704,17 +4728,17 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>C001733353</t>
+          <t>C004175937</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>C001733353 - CARRERO GUTIERREZ YEISER ESTEFANIA</t>
+          <t>C004175937 - DUAREZ DELGADO CRISTOBAL</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="I47" s="2" t="n">
@@ -4727,7 +4751,7 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
@@ -4737,26 +4761,14 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="N47" t="inlineStr"/>
       <c r="O47" t="inlineStr"/>
-      <c r="P47" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="Q47" t="inlineStr">
-        <is>
-          <t>Ninguna, entendió correctamente</t>
-        </is>
-      </c>
-      <c r="R47" t="inlineStr">
-        <is>
-          <t>Mejores promociones</t>
-        </is>
-      </c>
+      <c r="P47" t="inlineStr"/>
+      <c r="Q47" t="inlineStr"/>
+      <c r="R47" t="inlineStr"/>
       <c r="S47" t="inlineStr"/>
       <c r="T47" t="inlineStr">
         <is>
@@ -4788,7 +4800,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>No tiene tiempo para capacitarse</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -4798,17 +4810,17 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>C004172442</t>
+          <t>C004047923</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>C004172442 - CORPORACION E INVERSIONES GADIEL E.I.R.L</t>
+          <t>C004047923 - HERRERA BALLENA JACKELINE DEL PILAR</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="I48" s="2" t="n">
@@ -4821,7 +4833,7 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -4829,24 +4841,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
       <c r="N48" t="inlineStr"/>
       <c r="O48" t="inlineStr"/>
-      <c r="P48" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="Q48" t="inlineStr">
-        <is>
-          <t>Ninguna, entendió correctamente</t>
-        </is>
-      </c>
-      <c r="R48" t="inlineStr">
-        <is>
-          <t>Mejores promociones</t>
-        </is>
-      </c>
+      <c r="P48" t="inlineStr"/>
+      <c r="Q48" t="inlineStr"/>
+      <c r="R48" t="inlineStr"/>
       <c r="S48" t="inlineStr"/>
       <c r="T48" t="inlineStr">
         <is>
@@ -4878,7 +4882,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>No tiene tiempo para capacitarse</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -4888,17 +4892,17 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>C004175937</t>
+          <t>C001691214</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>C004175937 - DUAREZ DELGADO CRISTOBAL</t>
+          <t>C001691214 - SANCHEZ TEJADA DORIS</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="I49" s="2" t="n">
@@ -4911,7 +4915,7 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
@@ -4921,14 +4925,26 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="N49" t="inlineStr"/>
       <c r="O49" t="inlineStr"/>
-      <c r="P49" t="inlineStr"/>
-      <c r="Q49" t="inlineStr"/>
-      <c r="R49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>Ninguna, entendió correctamente</t>
+        </is>
+      </c>
+      <c r="R49" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
       <c r="S49" t="inlineStr"/>
       <c r="T49" t="inlineStr">
         <is>
@@ -4950,7 +4966,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>1000049464</t>
+          <t>1000009104</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -4960,7 +4976,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>No tiene tiempo para capacitarse</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -4970,17 +4986,17 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>C004161330</t>
+          <t>C001707748</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>C004161330 - FERNANDEZ ARCELA MILITZA JERSSUNNY</t>
+          <t>C001707748 - ESTELA GAMARRA PERCY</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="I50" s="2" t="n">
@@ -4993,7 +5009,7 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
@@ -5004,21 +5020,9 @@
       <c r="M50" t="inlineStr"/>
       <c r="N50" t="inlineStr"/>
       <c r="O50" t="inlineStr"/>
-      <c r="P50" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="Q50" t="inlineStr">
-        <is>
-          <t>Ninguna, entendió correctamente</t>
-        </is>
-      </c>
-      <c r="R50" t="inlineStr">
-        <is>
-          <t>Mejores promociones</t>
-        </is>
-      </c>
+      <c r="P50" t="inlineStr"/>
+      <c r="Q50" t="inlineStr"/>
+      <c r="R50" t="inlineStr"/>
       <c r="S50" t="inlineStr"/>
       <c r="T50" t="inlineStr">
         <is>
@@ -5060,12 +5064,12 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>C004222016</t>
+          <t>C001656801</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>C004222016 - MEJIA MESTANZA SHAROL LICETH</t>
+          <t>C001656801 - ZULOETA ZULOETA HENRY</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -5091,11 +5095,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
+      <c r="M51" t="inlineStr"/>
       <c r="N51" t="inlineStr"/>
       <c r="O51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
@@ -5144,7 +5144,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>No tiene tiempo para capacitarse</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -5154,17 +5154,17 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>C001717998</t>
+          <t>C004166743</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>C001717998 - MONTEZA FERNANDEZ MEDALI TEODOSIA</t>
+          <t>C004166743 - LLAMOSA ORMEÑO ORLANDO</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="I52" s="2" t="n">
@@ -5177,7 +5177,7 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
@@ -5185,28 +5185,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
+      <c r="M52" t="inlineStr"/>
       <c r="N52" t="inlineStr"/>
       <c r="O52" t="inlineStr"/>
-      <c r="P52" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="Q52" t="inlineStr">
-        <is>
-          <t>Ninguna, entendió correctamente</t>
-        </is>
-      </c>
-      <c r="R52" t="inlineStr">
-        <is>
-          <t>Mejores promociones</t>
-        </is>
-      </c>
+      <c r="P52" t="inlineStr"/>
+      <c r="Q52" t="inlineStr"/>
+      <c r="R52" t="inlineStr"/>
       <c r="S52" t="inlineStr"/>
       <c r="T52" t="inlineStr">
         <is>
@@ -5248,12 +5232,12 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>C004240362</t>
+          <t>C001668337</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>C004240362 - ALVAREZ SORIANO SILVIA PAOLA</t>
+          <t>C001668337 - ROJAS REQUEJO MARIA SILVIA</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -5279,7 +5263,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
       <c r="N53" t="inlineStr"/>
       <c r="O53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
@@ -5338,12 +5326,12 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>C001545229</t>
+          <t>C001715744</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>C001545229 - VALLEJOS DIAZ MARIA CANDELARIA</t>
+          <t>C001715744 - MONTALVO ZAVALETA MARIA MARIBEL</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -5390,17 +5378,13 @@
       <c r="S54" t="inlineStr"/>
       <c r="T54" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U54" t="inlineStr">
-        <is>
-          <t>Cliente</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr"/>
       <c r="V54" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>NO - No hizo pedido</t>
         </is>
       </c>
     </row>
@@ -5432,12 +5416,12 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>C001668337</t>
+          <t>C001717998</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>C001668337 - ROJAS REQUEJO MARIA SILVIA</t>
+          <t>C001717998 - MONTEZA FERNANDEZ MEDALI TEODOSIA</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -5506,7 +5490,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>1000049464</t>
+          <t>1000009104</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -5526,12 +5510,12 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>C001715744</t>
+          <t>C001085135</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>C001715744 - MONTALVO ZAVALETA MARIA MARIBEL</t>
+          <t>C001085135 - GUEVARA DE MANOSALVA MARIA TEONILA</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -5596,7 +5580,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>1000049464</t>
+          <t>1000009104</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -5616,12 +5600,12 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>C001487318</t>
+          <t>C001082245</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>C001487318 - HUACCHILLO VEGA DAISY</t>
+          <t>C001082245 - MECHAN TORRES JUANA</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -5700,7 +5684,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>No tiene tiempo para capacitarse</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -5710,17 +5694,17 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>C001703938</t>
+          <t>C001173492</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>C001703938 - ALDANA SALAZAR SHEYLA KARINA</t>
+          <t>C001173492 - OLIVERA GARCIA DE DIAZ DIANA</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="I58" s="2" t="n">
@@ -5733,7 +5717,7 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
@@ -5748,9 +5732,21 @@
       </c>
       <c r="N58" t="inlineStr"/>
       <c r="O58" t="inlineStr"/>
-      <c r="P58" t="inlineStr"/>
-      <c r="Q58" t="inlineStr"/>
-      <c r="R58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="Q58" t="inlineStr">
+        <is>
+          <t>Ninguna, entendió correctamente</t>
+        </is>
+      </c>
+      <c r="R58" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
       <c r="S58" t="inlineStr"/>
       <c r="T58" t="inlineStr">
         <is>
@@ -5792,12 +5788,12 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>C001165828</t>
+          <t>C001172980</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>C001165828 - JIMENEZ VALENCIA MARIA GLADYS</t>
+          <t>C001172980 - URIARTE VASQUEZ YENNY DEL ROCIO</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -5825,7 +5821,7 @@
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="N59" t="inlineStr"/>
@@ -5876,7 +5872,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>No tiene tiempo para capacitarse</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -5886,17 +5882,17 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>C001414604</t>
+          <t>C001180059</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>C001414604 - VASQUEZ RAMIREZ YENY CARINA</t>
+          <t>C001180059 - DAMIAN INONAN JORGE MERCEDES</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="I60" s="2" t="n">
@@ -5909,7 +5905,7 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
@@ -5920,35 +5916,19 @@
       <c r="M60" t="inlineStr"/>
       <c r="N60" t="inlineStr"/>
       <c r="O60" t="inlineStr"/>
-      <c r="P60" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="Q60" t="inlineStr">
-        <is>
-          <t>Ninguna, entendió correctamente</t>
-        </is>
-      </c>
-      <c r="R60" t="inlineStr">
-        <is>
-          <t>Mejores promociones</t>
-        </is>
-      </c>
+      <c r="P60" t="inlineStr"/>
+      <c r="Q60" t="inlineStr"/>
+      <c r="R60" t="inlineStr"/>
       <c r="S60" t="inlineStr"/>
       <c r="T60" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U60" t="inlineStr">
-        <is>
-          <t>Cliente</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr"/>
       <c r="V60" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>NO - No hizo pedido</t>
         </is>
       </c>
     </row>
@@ -5980,12 +5960,12 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>C001751925</t>
+          <t>C001545229</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>C001751925 - KININ TINCHO RAQUELINA</t>
+          <t>C001545229 - VALLEJOS DIAZ MARIA CANDELARIA</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -6011,11 +5991,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
+      <c r="M61" t="inlineStr"/>
       <c r="N61" t="inlineStr"/>
       <c r="O61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
@@ -6036,13 +6012,17 @@
       <c r="S61" t="inlineStr"/>
       <c r="T61" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U61" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
       <c r="V61" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -6074,12 +6054,12 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>C004166024</t>
+          <t>C004094224</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>C004166024 - SANTISTEBAN DE TINOCO EMMA</t>
+          <t>C004094224 - QUIROZ SANTISTEBAN KATHERIN DEL MILAGRO</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -6105,7 +6085,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
       <c r="N62" t="inlineStr"/>
       <c r="O62" t="inlineStr"/>
       <c r="P62" t="inlineStr"/>
@@ -6152,12 +6136,12 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>C004166739</t>
+          <t>C004167751</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>C004166739 - SANTISTEBAN ACOSTA CARMEN ROSA</t>
+          <t>C004167751 - MEZA CALDERON LUIS HENRY</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -6232,7 +6216,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>No tiene tiempo para capacitarse</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -6242,17 +6226,17 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>C004167751</t>
+          <t>C004166024</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>C004167751 - MEZA CALDERON LUIS HENRY</t>
+          <t>C004166024 - SANTISTEBAN DE TINOCO EMMA</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="I64" s="2" t="n">
@@ -6265,7 +6249,7 @@
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
@@ -6276,21 +6260,9 @@
       <c r="M64" t="inlineStr"/>
       <c r="N64" t="inlineStr"/>
       <c r="O64" t="inlineStr"/>
-      <c r="P64" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="Q64" t="inlineStr">
-        <is>
-          <t>Ninguna, entendió correctamente</t>
-        </is>
-      </c>
-      <c r="R64" t="inlineStr">
-        <is>
-          <t>Mejores promociones</t>
-        </is>
-      </c>
+      <c r="P64" t="inlineStr"/>
+      <c r="Q64" t="inlineStr"/>
+      <c r="R64" t="inlineStr"/>
       <c r="S64" t="inlineStr"/>
       <c r="T64" t="inlineStr">
         <is>
@@ -6322,7 +6294,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>No tiene tiempo para capacitarse</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -6332,17 +6304,17 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>C004094224</t>
+          <t>C004166739</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>C004094224 - QUIROZ SANTISTEBAN KATHERIN DEL MILAGRO</t>
+          <t>C004166739 - SANTISTEBAN ACOSTA CARMEN ROSA</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="I65" s="2" t="n">
@@ -6355,7 +6327,7 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
@@ -6363,16 +6335,24 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
+      <c r="M65" t="inlineStr"/>
       <c r="N65" t="inlineStr"/>
       <c r="O65" t="inlineStr"/>
-      <c r="P65" t="inlineStr"/>
-      <c r="Q65" t="inlineStr"/>
-      <c r="R65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="Q65" t="inlineStr">
+        <is>
+          <t>Ninguna, entendió correctamente</t>
+        </is>
+      </c>
+      <c r="R65" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
       <c r="S65" t="inlineStr"/>
       <c r="T65" t="inlineStr">
         <is>
@@ -6404,7 +6384,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>No tiene tiempo para capacitarse</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -6414,17 +6394,17 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>C004166743</t>
+          <t>C004240340</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>C004166743 - LLAMOSA ORMEÑO ORLANDO</t>
+          <t>C004240340 - RACHI TABOADA MAGDALENA</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="I66" s="2" t="n">
@@ -6437,7 +6417,7 @@
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
@@ -6448,9 +6428,21 @@
       <c r="M66" t="inlineStr"/>
       <c r="N66" t="inlineStr"/>
       <c r="O66" t="inlineStr"/>
-      <c r="P66" t="inlineStr"/>
-      <c r="Q66" t="inlineStr"/>
-      <c r="R66" t="inlineStr"/>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="Q66" t="inlineStr">
+        <is>
+          <t>Ninguna, entendió correctamente</t>
+        </is>
+      </c>
+      <c r="R66" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
       <c r="S66" t="inlineStr"/>
       <c r="T66" t="inlineStr">
         <is>
@@ -6492,12 +6484,12 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>C004240340</t>
+          <t>C004240362</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>C004240340 - RACHI TABOADA MAGDALENA</t>
+          <t>C004240362 - ALVAREZ SORIANO SILVIA PAOLA</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -6562,7 +6554,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>1000009104</t>
+          <t>1000049464</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -6582,12 +6574,12 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>C001085135</t>
+          <t>C001487318</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>C001085135 - GUEVARA DE MANOSALVA MARIA TEONILA</t>
+          <t>C001487318 - HUACCHILLO VEGA DAISY</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -6613,7 +6605,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
       <c r="N68" t="inlineStr"/>
       <c r="O68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
@@ -6672,12 +6668,12 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>C001082245</t>
+          <t>C001077387</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>C001082245 - MECHAN TORRES JUANA</t>
+          <t>C001077387 - CASUSOL DELGADO DE GARCIA ROSA AMELIA</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -6703,11 +6699,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
+      <c r="M69" t="inlineStr"/>
       <c r="N69" t="inlineStr"/>
       <c r="O69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
@@ -6746,7 +6738,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>1000009104</t>
+          <t>1000049464</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -6766,12 +6758,12 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>C001077387</t>
+          <t>C001308899</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>C001077387 - CASUSOL DELGADO DE GARCIA ROSA AMELIA</t>
+          <t>C001308899 - VASQUEZ SAUCEDO DE DIAZ ESTHER</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -6856,12 +6848,12 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>C001165821</t>
+          <t>C001414604</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>C001165821 - ALDUI GASTELO INES</t>
+          <t>C001414604 - VASQUEZ RAMIREZ YENY CARINA</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -6887,11 +6879,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
+      <c r="M71" t="inlineStr"/>
       <c r="N71" t="inlineStr"/>
       <c r="O71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
@@ -6912,13 +6900,17 @@
       <c r="S71" t="inlineStr"/>
       <c r="T71" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U71" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
       <c r="V71" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -6950,12 +6942,12 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>C001165908</t>
+          <t>C001165828</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>C001165908 - BANCES ENEQUE LADY MARIBEL</t>
+          <t>C001165828 - JIMENEZ VALENCIA MARIA GLADYS</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -6983,7 +6975,7 @@
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="N72" t="inlineStr"/>
@@ -7044,12 +7036,12 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>C001172980</t>
+          <t>C001165908</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>C001172980 - URIARTE VASQUEZ YENNY DEL ROCIO</t>
+          <t>C001165908 - BANCES ENEQUE LADY MARIBEL</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -7138,12 +7130,12 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>C001173492</t>
+          <t>C001751925</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>C001173492 - OLIVERA GARCIA DE DIAZ DIANA</t>
+          <t>C001751925 - KININ TINCHO RAQUELINA</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -7232,12 +7224,12 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>C001180059</t>
+          <t>C001703938</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>C001180059 - DAMIAN INONAN JORGE MERCEDES</t>
+          <t>C001703938 - ALDANA SALAZAR SHEYLA KARINA</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -7263,7 +7255,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M75" t="inlineStr"/>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
       <c r="N75" t="inlineStr"/>
       <c r="O75" t="inlineStr"/>
       <c r="P75" t="inlineStr"/>
@@ -7310,12 +7306,12 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>C001308899</t>
+          <t>C001165821</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>C001308899 - VASQUEZ SAUCEDO DE DIAZ ESTHER</t>
+          <t>C001165821 - ALDUI GASTELO INES</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -7341,7 +7337,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M76" t="inlineStr"/>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
       <c r="N76" t="inlineStr"/>
       <c r="O76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
@@ -9578,7 +9578,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>No tiene tiempo para capacitarse</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -9588,17 +9588,17 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>C004183371</t>
+          <t>C004237071</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>C004183371 - SORIANO MONTALVO WILIAN ALBERTO</t>
+          <t>C004237071 - IDROGO IDROGO REINELDA</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="I101" s="2" t="n">
@@ -9611,7 +9611,7 @@
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="L101" t="inlineStr">
@@ -9621,14 +9621,26 @@
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="N101" t="inlineStr"/>
       <c r="O101" t="inlineStr"/>
-      <c r="P101" t="inlineStr"/>
-      <c r="Q101" t="inlineStr"/>
-      <c r="R101" t="inlineStr"/>
+      <c r="P101" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="Q101" t="inlineStr">
+        <is>
+          <t>Ninguna, entendió correctamente</t>
+        </is>
+      </c>
+      <c r="R101" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
       <c r="S101" t="inlineStr"/>
       <c r="T101" t="inlineStr">
         <is>
@@ -9660,7 +9672,7 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>No tiene tiempo para capacitarse</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -9670,17 +9682,17 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>C004212544</t>
+          <t>C004183371</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>C004212544 - VASQUEZ REYES FANNY DEL PILAR</t>
+          <t>C004183371 - SORIANO MONTALVO WILIAN ALBERTO</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="I102" s="2" t="n">
@@ -9693,7 +9705,7 @@
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="L102" t="inlineStr">
@@ -9703,26 +9715,14 @@
       </c>
       <c r="M102" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="N102" t="inlineStr"/>
       <c r="O102" t="inlineStr"/>
-      <c r="P102" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="Q102" t="inlineStr">
-        <is>
-          <t>Ninguna, entendió correctamente</t>
-        </is>
-      </c>
-      <c r="R102" t="inlineStr">
-        <is>
-          <t>Apoyo del vendedor</t>
-        </is>
-      </c>
+      <c r="P102" t="inlineStr"/>
+      <c r="Q102" t="inlineStr"/>
+      <c r="R102" t="inlineStr"/>
       <c r="S102" t="inlineStr"/>
       <c r="T102" t="inlineStr">
         <is>
@@ -9764,12 +9764,12 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>C004237071</t>
+          <t>C004212544</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>C004237071 - IDROGO IDROGO REINELDA</t>
+          <t>C004212544 - VASQUEZ REYES FANNY DEL PILAR</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -9814,7 +9814,7 @@
       </c>
       <c r="R103" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Apoyo del vendedor</t>
         </is>
       </c>
       <c r="S103" t="inlineStr"/>
@@ -9838,7 +9838,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>1000049464</t>
+          <t>1000009104</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -9858,12 +9858,12 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>C001723810</t>
+          <t>C001733879</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>C001723810 - SANTOS TINEO MELISSA DE FATIMA</t>
+          <t>C001733879 - RODRIGUEZ BALCAZAR GINA OLENKA</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -9903,7 +9903,7 @@
       </c>
       <c r="Q104" t="inlineStr">
         <is>
-          <t>Iniciar sesión</t>
+          <t>Ninguna, entendió correctamente</t>
         </is>
       </c>
       <c r="R104" t="inlineStr">
@@ -9914,17 +9914,13 @@
       <c r="S104" t="inlineStr"/>
       <c r="T104" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U104" t="inlineStr">
-        <is>
-          <t>Cliente</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U104" t="inlineStr"/>
       <c r="V104" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>NO - No hizo pedido</t>
         </is>
       </c>
     </row>
@@ -10030,7 +10026,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>1000009104</t>
+          <t>1000049464</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -10050,12 +10046,12 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>C001733879</t>
+          <t>C001723810</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>C001733879 - RODRIGUEZ BALCAZAR GINA OLENKA</t>
+          <t>C001723810 - SANTOS TINEO MELISSA DE FATIMA</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -10095,7 +10091,7 @@
       </c>
       <c r="Q106" t="inlineStr">
         <is>
-          <t>Ninguna, entendió correctamente</t>
+          <t>Iniciar sesión</t>
         </is>
       </c>
       <c r="R106" t="inlineStr">
@@ -10106,13 +10102,17 @@
       <c r="S106" t="inlineStr"/>
       <c r="T106" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U106" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U106" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
       <c r="V106" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -10504,7 +10504,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>1000049464</t>
+          <t>1000009104</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -10524,12 +10524,12 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>C001400715</t>
+          <t>C001452822</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>C001400715 - GAMARRA SANCHEZ FREDDY</t>
+          <t>C001452822 - FERNANDEZ CABRERA LUISA</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -10580,13 +10580,17 @@
       <c r="S111" t="inlineStr"/>
       <c r="T111" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U111" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U111" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
       <c r="V111" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -10598,7 +10602,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>1000009104</t>
+          <t>1000049464</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -10618,12 +10622,12 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>C001452822</t>
+          <t>C001400715</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>C001452822 - FERNANDEZ CABRERA LUISA</t>
+          <t>C001400715 - GAMARRA SANCHEZ FREDDY</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -10674,17 +10678,13 @@
       <c r="S112" t="inlineStr"/>
       <c r="T112" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U112" t="inlineStr">
-        <is>
-          <t>Cliente</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U112" t="inlineStr"/>
       <c r="V112" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>NO - No hizo pedido</t>
         </is>
       </c>
     </row>
@@ -11558,7 +11558,7 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>1000009104</t>
+          <t>1000049464</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -11568,7 +11568,7 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>No tiene tiempo para capacitarse</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -11578,17 +11578,17 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>C004241151</t>
+          <t>C001075925</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>C004241151 - TERAN CAYAO MAGALY</t>
+          <t>C001075925 - OLIVARES REYES MARGARITA</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="I122" s="2" t="n">
@@ -11601,7 +11601,7 @@
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="L122" t="inlineStr">
@@ -11609,42 +11609,22 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M122" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
+      <c r="M122" t="inlineStr"/>
       <c r="N122" t="inlineStr"/>
       <c r="O122" t="inlineStr"/>
-      <c r="P122" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="Q122" t="inlineStr">
-        <is>
-          <t>Iniciar sesión</t>
-        </is>
-      </c>
-      <c r="R122" t="inlineStr">
-        <is>
-          <t>Mejores promociones</t>
-        </is>
-      </c>
+      <c r="P122" t="inlineStr"/>
+      <c r="Q122" t="inlineStr"/>
+      <c r="R122" t="inlineStr"/>
       <c r="S122" t="inlineStr"/>
       <c r="T122" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U122" t="inlineStr">
-        <is>
-          <t>Cliente</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U122" t="inlineStr"/>
       <c r="V122" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>NO - No hizo pedido</t>
         </is>
       </c>
     </row>
@@ -11666,7 +11646,7 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>No tiene tiempo para capacitarse</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -11676,17 +11656,17 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>C001075925</t>
+          <t>C001075936</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>C001075925 - OLIVARES REYES MARGARITA</t>
+          <t>C001075936 - FIESTAS BAZAN NELLY</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="I123" s="2" t="n">
@@ -11699,7 +11679,7 @@
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="L123" t="inlineStr">
@@ -11707,22 +11687,42 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M123" t="inlineStr"/>
+      <c r="M123" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
       <c r="N123" t="inlineStr"/>
       <c r="O123" t="inlineStr"/>
-      <c r="P123" t="inlineStr"/>
-      <c r="Q123" t="inlineStr"/>
-      <c r="R123" t="inlineStr"/>
+      <c r="P123" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="Q123" t="inlineStr">
+        <is>
+          <t>Ninguna, entendió correctamente</t>
+        </is>
+      </c>
+      <c r="R123" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
       <c r="S123" t="inlineStr"/>
       <c r="T123" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U123" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U123" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
       <c r="V123" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -11754,12 +11754,12 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>C001075936</t>
+          <t>C001076493</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>C001075936 - FIESTAS BAZAN NELLY</t>
+          <t>C001076493 - PEREZ ALARCON GEORGINA</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -11810,17 +11810,13 @@
       <c r="S124" t="inlineStr"/>
       <c r="T124" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U124" t="inlineStr">
-        <is>
-          <t>Cliente</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U124" t="inlineStr"/>
       <c r="V124" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>NO - No hizo pedido</t>
         </is>
       </c>
     </row>
@@ -11852,12 +11848,12 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>C001076493</t>
+          <t>C001076973</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>C001076493 - PEREZ ALARCON GEORGINA</t>
+          <t>C001076973 - FIESTAS BAZAN CECILIA PILAR</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -11885,7 +11881,7 @@
       </c>
       <c r="M125" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="N125" t="inlineStr"/>
@@ -11908,13 +11904,17 @@
       <c r="S125" t="inlineStr"/>
       <c r="T125" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U125" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U125" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
       <c r="V125" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -11946,12 +11946,12 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>C001076973</t>
+          <t>C001098581</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>C001076973 - FIESTAS BAZAN CECILIA PILAR</t>
+          <t>C001098581 - ROSALES RIOS PRUDENCIO JAIME</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -11979,7 +11979,7 @@
       </c>
       <c r="M126" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="N126" t="inlineStr"/>
@@ -12044,12 +12044,12 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>C001098581</t>
+          <t>C001649509</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>C001098581 - ROSALES RIOS PRUDENCIO JAIME</t>
+          <t>C001649509 - PANTA ARROYO ESTEFANI MERLYN</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -12077,7 +12077,7 @@
       </c>
       <c r="M127" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="N127" t="inlineStr"/>
@@ -12100,17 +12100,13 @@
       <c r="S127" t="inlineStr"/>
       <c r="T127" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U127" t="inlineStr">
-        <is>
-          <t>Cliente</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U127" t="inlineStr"/>
       <c r="V127" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>NO - No hizo pedido</t>
         </is>
       </c>
     </row>
@@ -12236,12 +12232,12 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>C001649509</t>
+          <t>C001761288</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>C001649509 - PANTA ARROYO ESTEFANI MERLYN</t>
+          <t>C001761288 - DAVILA FLORES LLAMI</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
@@ -12269,7 +12265,7 @@
       </c>
       <c r="M129" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="N129" t="inlineStr"/>
@@ -12292,13 +12288,17 @@
       <c r="S129" t="inlineStr"/>
       <c r="T129" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U129" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U129" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
       <c r="V129" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -12424,12 +12424,12 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>C001761288</t>
+          <t>C004047577</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>C001761288 - DAVILA FLORES LLAMI</t>
+          <t>C004047577 - CORREA DE CAMPOS CRISTINA</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
@@ -12522,12 +12522,12 @@
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>C004210654</t>
+          <t>C004165869</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>C004210654 - CHUGDEN CANCINO WALTER</t>
+          <t>C004165869 - PLACENCIA LEYTON ANA LAURA</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
@@ -12555,7 +12555,7 @@
       </c>
       <c r="M132" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="N132" t="inlineStr"/>
@@ -12596,7 +12596,7 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>1000049464</t>
+          <t>1000009104</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -12616,12 +12616,12 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>C004047577</t>
+          <t>C004241151</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>C004047577 - CORREA DE CAMPOS CRISTINA</t>
+          <t>C004241151 - TERAN CAYAO MAGALY</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
@@ -12649,7 +12649,7 @@
       </c>
       <c r="M133" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="N133" t="inlineStr"/>
@@ -12661,7 +12661,7 @@
       </c>
       <c r="Q133" t="inlineStr">
         <is>
-          <t>Ninguna, entendió correctamente</t>
+          <t>Iniciar sesión</t>
         </is>
       </c>
       <c r="R133" t="inlineStr">
@@ -12714,12 +12714,12 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>C004165869</t>
+          <t>C004210654</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>C004165869 - PLACENCIA LEYTON ANA LAURA</t>
+          <t>C004210654 - CHUGDEN CANCINO WALTER</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
@@ -12747,7 +12747,7 @@
       </c>
       <c r="M134" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="N134" t="inlineStr"/>
@@ -12974,7 +12974,7 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>No tiene tiempo para capacitarse</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
@@ -12984,17 +12984,17 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>C001483403</t>
+          <t>C001165904</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>C001483403 - CALDERON COBA GLADIS</t>
+          <t>C001165904 - VASQUEZ CUBAS MARIA LUCINA</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="I137" s="2" t="n">
@@ -13007,7 +13007,7 @@
       </c>
       <c r="K137" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="L137" t="inlineStr">
@@ -13022,21 +13022,9 @@
       </c>
       <c r="N137" t="inlineStr"/>
       <c r="O137" t="inlineStr"/>
-      <c r="P137" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="Q137" t="inlineStr">
-        <is>
-          <t>Ninguna, entendió correctamente</t>
-        </is>
-      </c>
-      <c r="R137" t="inlineStr">
-        <is>
-          <t>Mejores promociones</t>
-        </is>
-      </c>
+      <c r="P137" t="inlineStr"/>
+      <c r="Q137" t="inlineStr"/>
+      <c r="R137" t="inlineStr"/>
       <c r="S137" t="inlineStr"/>
       <c r="T137" t="inlineStr">
         <is>
@@ -13068,7 +13056,7 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>No tiene tiempo para capacitarse</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
@@ -13078,17 +13066,17 @@
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>C001165904</t>
+          <t>C001483403</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>C001165904 - VASQUEZ CUBAS MARIA LUCINA</t>
+          <t>C001483403 - CALDERON COBA GLADIS</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="I138" s="2" t="n">
@@ -13101,7 +13089,7 @@
       </c>
       <c r="K138" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="L138" t="inlineStr">
@@ -13116,9 +13104,21 @@
       </c>
       <c r="N138" t="inlineStr"/>
       <c r="O138" t="inlineStr"/>
-      <c r="P138" t="inlineStr"/>
-      <c r="Q138" t="inlineStr"/>
-      <c r="R138" t="inlineStr"/>
+      <c r="P138" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="Q138" t="inlineStr">
+        <is>
+          <t>Ninguna, entendió correctamente</t>
+        </is>
+      </c>
+      <c r="R138" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
       <c r="S138" t="inlineStr"/>
       <c r="T138" t="inlineStr">
         <is>
@@ -13258,12 +13258,12 @@
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>C001743638</t>
+          <t>C004180630</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>C001743638 - LLATAS IZQUIERDO YUDI</t>
+          <t>C004180630 - BARBOZA ZAMORA LILIANA</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
@@ -13298,7 +13298,7 @@
       <c r="O140" t="inlineStr"/>
       <c r="P140" t="inlineStr">
         <is>
-          <t>Algo dispuesto</t>
+          <t>Muy dispuesto</t>
         </is>
       </c>
       <c r="Q140" t="inlineStr">
@@ -13446,12 +13446,12 @@
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>C004180630</t>
+          <t>C001731912</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>C004180630 - BARBOZA ZAMORA LILIANA</t>
+          <t>C001731912 - GONZALES MONTEZA ERIKA JUDITH</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
@@ -13502,13 +13502,17 @@
       <c r="S142" t="inlineStr"/>
       <c r="T142" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U142" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U142" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
       <c r="V142" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -13540,12 +13544,12 @@
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>C001722004</t>
+          <t>C001734798</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>C001722004 - TERAN TAFUR MARGARITA</t>
+          <t>C001734798 - MANAYALLE CABRERA SILVIA ELIANA</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
@@ -13573,7 +13577,7 @@
       </c>
       <c r="M143" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="N143" t="inlineStr"/>
@@ -13596,13 +13600,17 @@
       <c r="S143" t="inlineStr"/>
       <c r="T143" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U143" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U143" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
       <c r="V143" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -13634,12 +13642,12 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>C001731912</t>
+          <t>C001736067</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>C001731912 - GONZALES MONTEZA ERIKA JUDITH</t>
+          <t>C001736067 - ANCAJIMA SARRIN JORGE ERICKSON</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
@@ -13665,11 +13673,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M144" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
+      <c r="M144" t="inlineStr"/>
       <c r="N144" t="inlineStr"/>
       <c r="O144" t="inlineStr"/>
       <c r="P144" t="inlineStr">
@@ -13732,12 +13736,12 @@
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>C001732991</t>
+          <t>C001736074</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>C001732991 - GASTULO ANTON ANA MARIA</t>
+          <t>C001736074 - AGIP SALAZAR ROSSANITA</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
@@ -13765,7 +13769,7 @@
       </c>
       <c r="M145" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="N145" t="inlineStr"/>
@@ -13777,7 +13781,7 @@
       </c>
       <c r="Q145" t="inlineStr">
         <is>
-          <t>Ninguna, entendió correctamente</t>
+          <t>Iniciar sesión</t>
         </is>
       </c>
       <c r="R145" t="inlineStr">
@@ -13788,17 +13792,13 @@
       <c r="S145" t="inlineStr"/>
       <c r="T145" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U145" t="inlineStr">
-        <is>
-          <t>Cliente</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U145" t="inlineStr"/>
       <c r="V145" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>NO - No hizo pedido</t>
         </is>
       </c>
     </row>
@@ -13830,12 +13830,12 @@
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>C001737386</t>
+          <t>C001732991</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>C001737386 - MONZON ORDINOLA MARITA ESTHER</t>
+          <t>C001732991 - GASTULO ANTON ANA MARIA</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
@@ -13861,7 +13861,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M146" t="inlineStr"/>
+      <c r="M146" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
       <c r="N146" t="inlineStr"/>
       <c r="O146" t="inlineStr"/>
       <c r="P146" t="inlineStr">
@@ -13887,12 +13891,12 @@
       </c>
       <c r="U146" t="inlineStr">
         <is>
-          <t>Nitro</t>
+          <t>Cliente</t>
         </is>
       </c>
       <c r="V146" t="inlineStr">
         <is>
-          <t>SI - Solo tiene pedido por Nitro</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -13924,12 +13928,12 @@
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>C001737414</t>
+          <t>C001737386</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>C001737414 - BRIONES DAMIAN LILA DEL CARMEN</t>
+          <t>C001737386 - MONZON ORDINOLA MARITA ESTHER</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
@@ -13955,11 +13959,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M147" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
+      <c r="M147" t="inlineStr"/>
       <c r="N147" t="inlineStr"/>
       <c r="O147" t="inlineStr"/>
       <c r="P147" t="inlineStr">
@@ -13985,12 +13985,12 @@
       </c>
       <c r="U147" t="inlineStr">
         <is>
-          <t>Cliente</t>
+          <t>Nitro</t>
         </is>
       </c>
       <c r="V147" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>SI - Solo tiene pedido por Nitro</t>
         </is>
       </c>
     </row>
@@ -14022,12 +14022,12 @@
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>C001734798</t>
+          <t>C001737414</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>C001734798 - MANAYALLE CABRERA SILVIA ELIANA</t>
+          <t>C001737414 - BRIONES DAMIAN LILA DEL CARMEN</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
@@ -14120,12 +14120,12 @@
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>C001736067</t>
+          <t>C001743638</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>C001736067 - ANCAJIMA SARRIN JORGE ERICKSON</t>
+          <t>C001743638 - LLATAS IZQUIERDO YUDI</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
@@ -14151,12 +14151,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M149" t="inlineStr"/>
+      <c r="M149" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
       <c r="N149" t="inlineStr"/>
       <c r="O149" t="inlineStr"/>
       <c r="P149" t="inlineStr">
         <is>
-          <t>Muy dispuesto</t>
+          <t>Algo dispuesto</t>
         </is>
       </c>
       <c r="Q149" t="inlineStr">
@@ -14172,17 +14176,13 @@
       <c r="S149" t="inlineStr"/>
       <c r="T149" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U149" t="inlineStr">
-        <is>
-          <t>Cliente</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U149" t="inlineStr"/>
       <c r="V149" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>NO - No hizo pedido</t>
         </is>
       </c>
     </row>
@@ -14214,12 +14214,12 @@
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>C001736074</t>
+          <t>C001680523</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>C001736074 - AGIP SALAZAR ROSSANITA</t>
+          <t>C001680523 - ALCANTARA HUERTAS SARA NOEMI</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
@@ -14259,7 +14259,7 @@
       </c>
       <c r="Q150" t="inlineStr">
         <is>
-          <t>Iniciar sesión</t>
+          <t>Ninguna, entendió correctamente</t>
         </is>
       </c>
       <c r="R150" t="inlineStr">
@@ -14270,13 +14270,17 @@
       <c r="S150" t="inlineStr"/>
       <c r="T150" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U150" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U150" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
       <c r="V150" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -14308,12 +14312,12 @@
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>C001680523</t>
+          <t>C001722004</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>C001680523 - ALCANTARA HUERTAS SARA NOEMI</t>
+          <t>C001722004 - TERAN TAFUR MARGARITA</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
@@ -14364,17 +14368,13 @@
       <c r="S151" t="inlineStr"/>
       <c r="T151" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U151" t="inlineStr">
-        <is>
-          <t>Cliente</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U151" t="inlineStr"/>
       <c r="V151" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>NO - No hizo pedido</t>
         </is>
       </c>
     </row>
@@ -14386,7 +14386,7 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>1000049464</t>
+          <t>1000009104</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -14396,7 +14396,7 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>No tiene tiempo para capacitarse</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
@@ -14406,17 +14406,17 @@
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>C001580128</t>
+          <t>C004243043</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>C001580128 - ROMERO GUEVARA ANA LUCILA</t>
+          <t>C004243043 - CONDORI DELGADO RENZO</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="I152" s="2" t="n">
@@ -14429,7 +14429,7 @@
       </c>
       <c r="K152" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="L152" t="inlineStr">
@@ -14444,9 +14444,21 @@
       </c>
       <c r="N152" t="inlineStr"/>
       <c r="O152" t="inlineStr"/>
-      <c r="P152" t="inlineStr"/>
-      <c r="Q152" t="inlineStr"/>
-      <c r="R152" t="inlineStr"/>
+      <c r="P152" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="Q152" t="inlineStr">
+        <is>
+          <t>Ninguna, entendió correctamente</t>
+        </is>
+      </c>
+      <c r="R152" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
       <c r="S152" t="inlineStr"/>
       <c r="T152" t="inlineStr">
         <is>
@@ -14468,7 +14480,7 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>1000009104</t>
+          <t>1000049464</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -14488,12 +14500,12 @@
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>C004243043</t>
+          <t>C004165256</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>C004243043 - CONDORI DELGADO RENZO</t>
+          <t>C004165256 - GONZALES LLONTOP JENNY DORIS</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
@@ -14521,7 +14533,7 @@
       </c>
       <c r="M153" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="N153" t="inlineStr"/>
@@ -14582,12 +14594,12 @@
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>C004165256</t>
+          <t>C004168197</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>C004165256 - GONZALES LLONTOP JENNY DORIS</t>
+          <t>C004168197 - LOPEZ FIESTAS MARCELINO JUNIOR</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
@@ -14615,7 +14627,7 @@
       </c>
       <c r="M154" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="N154" t="inlineStr"/>
@@ -14666,7 +14678,7 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>No tiene tiempo para capacitarse</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
@@ -14676,17 +14688,17 @@
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>C004168197</t>
+          <t>C001580128</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>C004168197 - LOPEZ FIESTAS MARCELINO JUNIOR</t>
+          <t>C001580128 - ROMERO GUEVARA ANA LUCILA</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="I155" s="2" t="n">
@@ -14699,7 +14711,7 @@
       </c>
       <c r="K155" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="L155" t="inlineStr">
@@ -14714,21 +14726,9 @@
       </c>
       <c r="N155" t="inlineStr"/>
       <c r="O155" t="inlineStr"/>
-      <c r="P155" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="Q155" t="inlineStr">
-        <is>
-          <t>Ninguna, entendió correctamente</t>
-        </is>
-      </c>
-      <c r="R155" t="inlineStr">
-        <is>
-          <t>Mejores promociones</t>
-        </is>
-      </c>
+      <c r="P155" t="inlineStr"/>
+      <c r="Q155" t="inlineStr"/>
+      <c r="R155" t="inlineStr"/>
       <c r="S155" t="inlineStr"/>
       <c r="T155" t="inlineStr">
         <is>
@@ -15216,7 +15216,7 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>1000009104</t>
+          <t>1000049464</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -15236,12 +15236,12 @@
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>C004203576</t>
+          <t>C001766275</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>C004203576 - BENAVIDES FIGUEROA MARLENY</t>
+          <t>C001766275 - PALOMINO TORRES SEGUNDO BRAYAN</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
@@ -15276,7 +15276,7 @@
       <c r="O161" t="inlineStr"/>
       <c r="P161" t="inlineStr">
         <is>
-          <t>Muy dispuesto</t>
+          <t>Nada dispuesto</t>
         </is>
       </c>
       <c r="Q161" t="inlineStr">
@@ -15292,13 +15292,17 @@
       <c r="S161" t="inlineStr"/>
       <c r="T161" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U161" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U161" t="inlineStr">
+        <is>
+          <t>Nitro</t>
+        </is>
+      </c>
       <c r="V161" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Solo tiene pedido por Nitro</t>
         </is>
       </c>
     </row>
@@ -15310,7 +15314,7 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>1000049464</t>
+          <t>1000009104</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -15330,12 +15334,12 @@
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>C001766275</t>
+          <t>C001709707</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>C001766275 - PALOMINO TORRES SEGUNDO BRAYAN</t>
+          <t>C001709707 - RODRIGUEZ RODRIGUEZ JUAN BACILINO</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
@@ -15363,14 +15367,14 @@
       </c>
       <c r="M162" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="N162" t="inlineStr"/>
       <c r="O162" t="inlineStr"/>
       <c r="P162" t="inlineStr">
         <is>
-          <t>Nada dispuesto</t>
+          <t>Algo dispuesto</t>
         </is>
       </c>
       <c r="Q162" t="inlineStr">
@@ -15391,12 +15395,12 @@
       </c>
       <c r="U162" t="inlineStr">
         <is>
-          <t>Nitro</t>
+          <t>Cliente</t>
         </is>
       </c>
       <c r="V162" t="inlineStr">
         <is>
-          <t>SI - Solo tiene pedido por Nitro</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -15428,12 +15432,12 @@
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>C001709707</t>
+          <t>C004203576</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>C001709707 - RODRIGUEZ RODRIGUEZ JUAN BACILINO</t>
+          <t>C004203576 - BENAVIDES FIGUEROA MARLENY</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
@@ -15461,14 +15465,14 @@
       </c>
       <c r="M163" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="N163" t="inlineStr"/>
       <c r="O163" t="inlineStr"/>
       <c r="P163" t="inlineStr">
         <is>
-          <t>Algo dispuesto</t>
+          <t>Muy dispuesto</t>
         </is>
       </c>
       <c r="Q163" t="inlineStr">
@@ -15484,17 +15488,13 @@
       <c r="S163" t="inlineStr"/>
       <c r="T163" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U163" t="inlineStr">
-        <is>
-          <t>Cliente</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U163" t="inlineStr"/>
       <c r="V163" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>NO - No hizo pedido</t>
         </is>
       </c>
     </row>
@@ -16154,7 +16154,7 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>No tiene tiempo para capacitarse</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
@@ -16164,17 +16164,17 @@
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>C001452413</t>
+          <t>C001079722</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>C001452413 - CHANDUVI PUICON SONIA VIOLETA</t>
+          <t>C001079722 - VASQUEZ CAPU AY MANUEL</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="I171" s="2" t="n">
@@ -16187,7 +16187,7 @@
       </c>
       <c r="K171" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="L171" t="inlineStr">
@@ -16195,12 +16195,28 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M171" t="inlineStr"/>
+      <c r="M171" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
       <c r="N171" t="inlineStr"/>
       <c r="O171" t="inlineStr"/>
-      <c r="P171" t="inlineStr"/>
-      <c r="Q171" t="inlineStr"/>
-      <c r="R171" t="inlineStr"/>
+      <c r="P171" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="Q171" t="inlineStr">
+        <is>
+          <t>Ninguna, entendió correctamente</t>
+        </is>
+      </c>
+      <c r="R171" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
       <c r="S171" t="inlineStr"/>
       <c r="T171" t="inlineStr">
         <is>
@@ -16246,12 +16262,12 @@
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>C001361475</t>
+          <t>C001081307</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>C001361475 - CORNEJO CHUMIOQUE MARIA OFELIA</t>
+          <t>C001081307 - SANTISTEBAN SANCHEZ VIOLETA</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
@@ -16282,7 +16298,7 @@
       <c r="O172" t="inlineStr"/>
       <c r="P172" t="inlineStr">
         <is>
-          <t>Algo dispuesto</t>
+          <t>Muy dispuesto</t>
         </is>
       </c>
       <c r="Q172" t="inlineStr">
@@ -16292,19 +16308,23 @@
       </c>
       <c r="R172" t="inlineStr">
         <is>
-          <t>Más confianza en la entrega</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
       <c r="S172" t="inlineStr"/>
       <c r="T172" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U172" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U172" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
       <c r="V172" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -16336,12 +16356,12 @@
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>C001079722</t>
+          <t>C001361475</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>C001079722 - VASQUEZ CAPU AY MANUEL</t>
+          <t>C001361475 - CORNEJO CHUMIOQUE MARIA OFELIA</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
@@ -16367,16 +16387,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M173" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
+      <c r="M173" t="inlineStr"/>
       <c r="N173" t="inlineStr"/>
       <c r="O173" t="inlineStr"/>
       <c r="P173" t="inlineStr">
         <is>
-          <t>Muy dispuesto</t>
+          <t>Algo dispuesto</t>
         </is>
       </c>
       <c r="Q173" t="inlineStr">
@@ -16386,23 +16402,19 @@
       </c>
       <c r="R173" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Más confianza en la entrega</t>
         </is>
       </c>
       <c r="S173" t="inlineStr"/>
       <c r="T173" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U173" t="inlineStr">
-        <is>
-          <t>Cliente</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U173" t="inlineStr"/>
       <c r="V173" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>NO - No hizo pedido</t>
         </is>
       </c>
     </row>
@@ -16424,7 +16436,7 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>No tiene tiempo para capacitarse</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
@@ -16434,17 +16446,17 @@
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>C001081307</t>
+          <t>C001452413</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>C001081307 - SANTISTEBAN SANCHEZ VIOLETA</t>
+          <t>C001452413 - CHANDUVI PUICON SONIA VIOLETA</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="I174" s="2" t="n">
@@ -16457,7 +16469,7 @@
       </c>
       <c r="K174" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="L174" t="inlineStr">
@@ -16468,21 +16480,9 @@
       <c r="M174" t="inlineStr"/>
       <c r="N174" t="inlineStr"/>
       <c r="O174" t="inlineStr"/>
-      <c r="P174" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="Q174" t="inlineStr">
-        <is>
-          <t>Ninguna, entendió correctamente</t>
-        </is>
-      </c>
-      <c r="R174" t="inlineStr">
-        <is>
-          <t>Mejores promociones</t>
-        </is>
-      </c>
+      <c r="P174" t="inlineStr"/>
+      <c r="Q174" t="inlineStr"/>
+      <c r="R174" t="inlineStr"/>
       <c r="S174" t="inlineStr"/>
       <c r="T174" t="inlineStr">
         <is>
@@ -16518,7 +16518,7 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>No tiene tiempo para capacitarse</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
@@ -16528,17 +16528,17 @@
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>C001696221</t>
+          <t>C001745658</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>C001696221 - VENTURA SUCLUPE MARIA FILOMENA</t>
+          <t>C001745658 - BRAVO PISCOYA MARIA GRIMALDINA</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="I175" s="2" t="n">
@@ -16551,7 +16551,7 @@
       </c>
       <c r="K175" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="L175" t="inlineStr">
@@ -16559,24 +16559,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M175" t="inlineStr"/>
+      <c r="M175" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
       <c r="N175" t="inlineStr"/>
       <c r="O175" t="inlineStr"/>
-      <c r="P175" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="Q175" t="inlineStr">
-        <is>
-          <t>Ninguna, entendió correctamente</t>
-        </is>
-      </c>
-      <c r="R175" t="inlineStr">
-        <is>
-          <t>Mejores promociones</t>
-        </is>
-      </c>
+      <c r="P175" t="inlineStr"/>
+      <c r="Q175" t="inlineStr"/>
+      <c r="R175" t="inlineStr"/>
       <c r="S175" t="inlineStr"/>
       <c r="T175" t="inlineStr">
         <is>
@@ -16612,7 +16604,7 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>No tiene tiempo para capacitarse</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
@@ -16622,17 +16614,17 @@
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>C001745658</t>
+          <t>C001696221</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>C001745658 - BRAVO PISCOYA MARIA GRIMALDINA</t>
+          <t>C001696221 - VENTURA SUCLUPE MARIA FILOMENA</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="I176" s="2" t="n">
@@ -16645,7 +16637,7 @@
       </c>
       <c r="K176" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="L176" t="inlineStr">
@@ -16653,16 +16645,24 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M176" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
+      <c r="M176" t="inlineStr"/>
       <c r="N176" t="inlineStr"/>
       <c r="O176" t="inlineStr"/>
-      <c r="P176" t="inlineStr"/>
-      <c r="Q176" t="inlineStr"/>
-      <c r="R176" t="inlineStr"/>
+      <c r="P176" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="Q176" t="inlineStr">
+        <is>
+          <t>Ninguna, entendió correctamente</t>
+        </is>
+      </c>
+      <c r="R176" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
       <c r="S176" t="inlineStr"/>
       <c r="T176" t="inlineStr">
         <is>
@@ -16802,12 +16802,12 @@
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>C004168885</t>
+          <t>C004166296</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>C004168885 - OLIVOS DE VIDAURRE ROSA</t>
+          <t>C004166296 - BRIONES SUSANIVAR RUDY GIAMPIER</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
@@ -16833,11 +16833,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M178" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
+      <c r="M178" t="inlineStr"/>
       <c r="N178" t="inlineStr"/>
       <c r="O178" t="inlineStr"/>
       <c r="P178" t="inlineStr">
@@ -16858,13 +16854,17 @@
       <c r="S178" t="inlineStr"/>
       <c r="T178" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U178" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U178" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
       <c r="V178" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -16896,12 +16896,12 @@
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>C004166296</t>
+          <t>C004168885</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>C004166296 - BRIONES SUSANIVAR RUDY GIAMPIER</t>
+          <t>C004168885 - OLIVOS DE VIDAURRE ROSA</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
@@ -16927,7 +16927,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M179" t="inlineStr"/>
+      <c r="M179" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
       <c r="N179" t="inlineStr"/>
       <c r="O179" t="inlineStr"/>
       <c r="P179" t="inlineStr">
@@ -16948,17 +16952,13 @@
       <c r="S179" t="inlineStr"/>
       <c r="T179" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U179" t="inlineStr">
-        <is>
-          <t>Cliente</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U179" t="inlineStr"/>
       <c r="V179" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>NO - No hizo pedido</t>
         </is>
       </c>
     </row>
@@ -17078,7 +17078,7 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>No tiene tiempo para capacitarse</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
@@ -17088,17 +17088,17 @@
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>C001669258</t>
+          <t>C004167512</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>C001669258 - HUAMAN CARLOS JENY AMELIA</t>
+          <t>C004167512 - DELGADO GONZALES ANACELI MARLI</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="I181" s="2" t="n">
@@ -17111,7 +17111,7 @@
       </c>
       <c r="K181" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="L181" t="inlineStr">
@@ -17122,19 +17122,35 @@
       <c r="M181" t="inlineStr"/>
       <c r="N181" t="inlineStr"/>
       <c r="O181" t="inlineStr"/>
-      <c r="P181" t="inlineStr"/>
-      <c r="Q181" t="inlineStr"/>
-      <c r="R181" t="inlineStr"/>
+      <c r="P181" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="Q181" t="inlineStr">
+        <is>
+          <t>Ninguna, entendió correctamente</t>
+        </is>
+      </c>
+      <c r="R181" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
       <c r="S181" t="inlineStr"/>
       <c r="T181" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U181" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U181" t="inlineStr">
+        <is>
+          <t>Nitro</t>
+        </is>
+      </c>
       <c r="V181" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Solo tiene pedido por Nitro</t>
         </is>
       </c>
     </row>
@@ -17248,12 +17264,12 @@
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>C004167512</t>
+          <t>C001550158</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>C004167512 - DELGADO GONZALES ANACELI MARLI</t>
+          <t>C001550158 - TORRES RODAS JESSICA NOEMI</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
@@ -17284,7 +17300,7 @@
       <c r="O183" t="inlineStr"/>
       <c r="P183" t="inlineStr">
         <is>
-          <t>Muy dispuesto</t>
+          <t>Algo dispuesto</t>
         </is>
       </c>
       <c r="Q183" t="inlineStr">
@@ -17342,12 +17358,12 @@
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>C001550158</t>
+          <t>C001405878</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>C001550158 - TORRES RODAS JESSICA NOEMI</t>
+          <t>C001405878 - FLORES OLIVA HUGO</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
@@ -17378,7 +17394,7 @@
       <c r="O184" t="inlineStr"/>
       <c r="P184" t="inlineStr">
         <is>
-          <t>Algo dispuesto</t>
+          <t>Muy dispuesto</t>
         </is>
       </c>
       <c r="Q184" t="inlineStr">
@@ -17399,12 +17415,12 @@
       </c>
       <c r="U184" t="inlineStr">
         <is>
-          <t>Nitro</t>
+          <t>Cliente</t>
         </is>
       </c>
       <c r="V184" t="inlineStr">
         <is>
-          <t>SI - Solo tiene pedido por Nitro</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -17436,12 +17452,12 @@
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>C001405878</t>
+          <t>C001173438</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>C001405878 - FLORES OLIVA HUGO</t>
+          <t>C001173438 - RIOS HERRERA MARIA ELOISA</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
@@ -17510,7 +17526,7 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>1000049464</t>
+          <t>1000009104</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -17530,12 +17546,12 @@
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>C001173438</t>
+          <t>C001628093</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>C001173438 - RIOS HERRERA MARIA ELOISA</t>
+          <t>C001628093 - CRUZ MORANTE LUIS</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
@@ -17624,12 +17640,12 @@
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>C001628093</t>
+          <t>C001740301</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>C001628093 - CRUZ MORANTE LUIS</t>
+          <t>C001740301 - GUERRERO PAREDES MERCEDES ISABEL</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
@@ -17698,7 +17714,7 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>1000009104</t>
+          <t>1000049464</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -17718,12 +17734,12 @@
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>C001740301</t>
+          <t>C001082733</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>C001740301 - GUERRERO PAREDES MERCEDES ISABEL</t>
+          <t>C001082733 - DAVILA RUIZ RAMIRO</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
@@ -17775,12 +17791,12 @@
       </c>
       <c r="U188" t="inlineStr">
         <is>
-          <t>Cliente</t>
+          <t>Nitro</t>
         </is>
       </c>
       <c r="V188" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>SI - Solo tiene pedido por Nitro</t>
         </is>
       </c>
     </row>
@@ -17906,12 +17922,12 @@
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>C001082733</t>
+          <t>C001224721</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>C001082733 - DAVILA RUIZ RAMIRO</t>
+          <t>C001224721 - ROJAS PRAVIA MARIA MERCEDES</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
@@ -17963,12 +17979,12 @@
       </c>
       <c r="U190" t="inlineStr">
         <is>
-          <t>Nitro</t>
+          <t>Cliente</t>
         </is>
       </c>
       <c r="V190" t="inlineStr">
         <is>
-          <t>SI - Solo tiene pedido por Nitro</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -18000,12 +18016,12 @@
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>C001224721</t>
+          <t>C001274655</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>C001224721 - ROJAS PRAVIA MARIA MERCEDES</t>
+          <t>C001274655 - MARTINEZ SOPLAPUCO PEDRO</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
@@ -18031,7 +18047,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M191" t="inlineStr"/>
+      <c r="M191" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
       <c r="N191" t="inlineStr"/>
       <c r="O191" t="inlineStr"/>
       <c r="P191" t="inlineStr">
@@ -18094,12 +18114,12 @@
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>C001274655</t>
+          <t>C001301555</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>C001274655 - MARTINEZ SOPLAPUCO PEDRO</t>
+          <t>C001301555 - AGURTO SANTOS JESSICA</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
@@ -18125,11 +18145,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M192" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
+      <c r="M192" t="inlineStr"/>
       <c r="N192" t="inlineStr"/>
       <c r="O192" t="inlineStr"/>
       <c r="P192" t="inlineStr">
@@ -18192,12 +18208,12 @@
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>C001301555</t>
+          <t>C001521360</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>C001301555 - AGURTO SANTOS JESSICA</t>
+          <t>C001521360 - CARLOS DE LA CRUZ SERGIO</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
@@ -18286,12 +18302,12 @@
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>C001521360</t>
+          <t>C001553531</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>C001521360 - CARLOS DE LA CRUZ SERGIO</t>
+          <t>C001553531 - RIVAS ARRIAGA JOSE RICARDO</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
@@ -18370,7 +18386,7 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>No tiene tiempo para capacitarse</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
@@ -18380,17 +18396,17 @@
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>C001553531</t>
+          <t>C001669258</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>C001553531 - RIVAS ARRIAGA JOSE RICARDO</t>
+          <t>C001669258 - HUAMAN CARLOS JENY AMELIA</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="I195" s="2" t="n">
@@ -18403,7 +18419,7 @@
       </c>
       <c r="K195" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="L195" t="inlineStr">
@@ -18414,35 +18430,19 @@
       <c r="M195" t="inlineStr"/>
       <c r="N195" t="inlineStr"/>
       <c r="O195" t="inlineStr"/>
-      <c r="P195" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="Q195" t="inlineStr">
-        <is>
-          <t>Ninguna, entendió correctamente</t>
-        </is>
-      </c>
-      <c r="R195" t="inlineStr">
-        <is>
-          <t>Mejores promociones</t>
-        </is>
-      </c>
+      <c r="P195" t="inlineStr"/>
+      <c r="Q195" t="inlineStr"/>
+      <c r="R195" t="inlineStr"/>
       <c r="S195" t="inlineStr"/>
       <c r="T195" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U195" t="inlineStr">
-        <is>
-          <t>Cliente</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U195" t="inlineStr"/>
       <c r="V195" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>NO - No hizo pedido</t>
         </is>
       </c>
     </row>
@@ -18892,7 +18892,7 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>1000009104</t>
+          <t>1000049464</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
@@ -18912,12 +18912,12 @@
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>C001661905</t>
+          <t>C001655917</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>C001661905 - GRADOS VENTOSILLA MARISOL</t>
+          <t>C001655917 - CHINCHAY VALENCIA MARIA CLEOFILDA</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
@@ -18945,19 +18945,19 @@
       </c>
       <c r="M201" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="N201" t="inlineStr"/>
       <c r="O201" t="inlineStr"/>
       <c r="P201" t="inlineStr">
         <is>
-          <t>Algo dispuesto</t>
+          <t>Muy dispuesto</t>
         </is>
       </c>
       <c r="Q201" t="inlineStr">
         <is>
-          <t>Ver promociones</t>
+          <t>Ninguna, entendió correctamente</t>
         </is>
       </c>
       <c r="R201" t="inlineStr">
@@ -18990,7 +18990,7 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>1000049464</t>
+          <t>1000009104</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
@@ -19010,12 +19010,12 @@
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>C001655917</t>
+          <t>C001661905</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>C001655917 - CHINCHAY VALENCIA MARIA CLEOFILDA</t>
+          <t>C001661905 - GRADOS VENTOSILLA MARISOL</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
@@ -19043,19 +19043,19 @@
       </c>
       <c r="M202" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="N202" t="inlineStr"/>
       <c r="O202" t="inlineStr"/>
       <c r="P202" t="inlineStr">
         <is>
-          <t>Muy dispuesto</t>
+          <t>Algo dispuesto</t>
         </is>
       </c>
       <c r="Q202" t="inlineStr">
         <is>
-          <t>Ninguna, entendió correctamente</t>
+          <t>Ver promociones</t>
         </is>
       </c>
       <c r="R202" t="inlineStr">
@@ -19816,12 +19816,12 @@
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>C001216357</t>
+          <t>C001088415</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>C001216357 - CRUZ MEZA NELLY AIDEE</t>
+          <t>C001088415 - JUAREZ VELASCO ROSA MARIA</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
@@ -19852,7 +19852,7 @@
       <c r="O211" t="inlineStr"/>
       <c r="P211" t="inlineStr">
         <is>
-          <t>Muy dispuesto</t>
+          <t>Algo dispuesto</t>
         </is>
       </c>
       <c r="Q211" t="inlineStr">
@@ -19900,7 +19900,7 @@
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>No tiene tiempo para capacitarse</t>
         </is>
       </c>
       <c r="E212" t="inlineStr">
@@ -19910,17 +19910,17 @@
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>C001088415</t>
+          <t>C001079831</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>C001088415 - JUAREZ VELASCO ROSA MARIA</t>
+          <t>C001079831 - LLONTO CAJUSOL MARIA LINDAURA</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="I212" s="2" t="n">
@@ -19933,7 +19933,7 @@
       </c>
       <c r="K212" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="L212" t="inlineStr">
@@ -19944,21 +19944,9 @@
       <c r="M212" t="inlineStr"/>
       <c r="N212" t="inlineStr"/>
       <c r="O212" t="inlineStr"/>
-      <c r="P212" t="inlineStr">
-        <is>
-          <t>Algo dispuesto</t>
-        </is>
-      </c>
-      <c r="Q212" t="inlineStr">
-        <is>
-          <t>Ninguna, entendió correctamente</t>
-        </is>
-      </c>
-      <c r="R212" t="inlineStr">
-        <is>
-          <t>Mejores promociones</t>
-        </is>
-      </c>
+      <c r="P212" t="inlineStr"/>
+      <c r="Q212" t="inlineStr"/>
+      <c r="R212" t="inlineStr"/>
       <c r="S212" t="inlineStr"/>
       <c r="T212" t="inlineStr">
         <is>
@@ -19984,7 +19972,7 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>1000049464</t>
+          <t>1000009104</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
@@ -19994,7 +19982,7 @@
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>No tiene tiempo para capacitarse</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E213" t="inlineStr">
@@ -20004,17 +19992,17 @@
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>C001079831</t>
+          <t>C001079729</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>C001079831 - LLONTO CAJUSOL MARIA LINDAURA</t>
+          <t>C001079729 - DUEÑAS DIAZ ROBERTO</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="I213" s="2" t="n">
@@ -20027,7 +20015,7 @@
       </c>
       <c r="K213" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="L213" t="inlineStr">
@@ -20038,9 +20026,21 @@
       <c r="M213" t="inlineStr"/>
       <c r="N213" t="inlineStr"/>
       <c r="O213" t="inlineStr"/>
-      <c r="P213" t="inlineStr"/>
-      <c r="Q213" t="inlineStr"/>
-      <c r="R213" t="inlineStr"/>
+      <c r="P213" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="Q213" t="inlineStr">
+        <is>
+          <t>Ninguna, entendió correctamente</t>
+        </is>
+      </c>
+      <c r="R213" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
       <c r="S213" t="inlineStr"/>
       <c r="T213" t="inlineStr">
         <is>
@@ -20066,7 +20066,7 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>1000009104</t>
+          <t>1000049464</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
@@ -20086,12 +20086,12 @@
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>C001079729</t>
+          <t>C001216357</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>C001079729 - DUEÑAS DIAZ ROBERTO</t>
+          <t>C001216357 - CRUZ MEZA NELLY AIDEE</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
@@ -20160,7 +20160,7 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>1000009104</t>
+          <t>1000049464</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
@@ -20180,12 +20180,12 @@
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>C004218405</t>
+          <t>C004237053</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>C004218405 - SUCLUPE LOPEZ WILLIAN ALBERTO</t>
+          <t>C004237053 - MENDO LLAGUENTO FANNY ISABEL</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
@@ -20211,11 +20211,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M215" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
+      <c r="M215" t="inlineStr"/>
       <c r="N215" t="inlineStr"/>
       <c r="O215" t="inlineStr"/>
       <c r="P215" t="inlineStr">
@@ -20258,7 +20254,7 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>1000049464</t>
+          <t>1000009104</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
@@ -20278,12 +20274,12 @@
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>C004237053</t>
+          <t>C004218405</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>C004237053 - MENDO LLAGUENTO FANNY ISABEL</t>
+          <t>C004218405 - SUCLUPE LOPEZ WILLIAN ALBERTO</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
@@ -20309,7 +20305,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M216" t="inlineStr"/>
+      <c r="M216" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
       <c r="N216" t="inlineStr"/>
       <c r="O216" t="inlineStr"/>
       <c r="P216" t="inlineStr">
@@ -20722,7 +20722,7 @@
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>No tiene tiempo para capacitarse</t>
         </is>
       </c>
       <c r="E221" t="inlineStr">
@@ -20732,17 +20732,17 @@
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>C001733149</t>
+          <t>C001735365</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>C001733149 - HUAMAN EXEBIO BERTHA ROSA</t>
+          <t>C001735365 - PUMA GALVEZ VERONICA</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="I221" s="2" t="n">
@@ -20755,7 +20755,7 @@
       </c>
       <c r="K221" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="L221" t="inlineStr">
@@ -20763,28 +20763,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M221" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
+      <c r="M221" t="inlineStr"/>
       <c r="N221" t="inlineStr"/>
       <c r="O221" t="inlineStr"/>
-      <c r="P221" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="Q221" t="inlineStr">
-        <is>
-          <t>Ninguna, entendió correctamente</t>
-        </is>
-      </c>
-      <c r="R221" t="inlineStr">
-        <is>
-          <t>Mejores promociones</t>
-        </is>
-      </c>
+      <c r="P221" t="inlineStr"/>
+      <c r="Q221" t="inlineStr"/>
+      <c r="R221" t="inlineStr"/>
       <c r="S221" t="inlineStr"/>
       <c r="T221" t="inlineStr">
         <is>
@@ -20816,7 +20800,7 @@
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>No tiene tiempo para capacitarse</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E222" t="inlineStr">
@@ -20826,17 +20810,17 @@
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>C001735365</t>
+          <t>C001733149</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>C001735365 - PUMA GALVEZ VERONICA</t>
+          <t>C001733149 - HUAMAN EXEBIO BERTHA ROSA</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="I222" s="2" t="n">
@@ -20849,7 +20833,7 @@
       </c>
       <c r="K222" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="L222" t="inlineStr">
@@ -20857,12 +20841,28 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M222" t="inlineStr"/>
+      <c r="M222" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
       <c r="N222" t="inlineStr"/>
       <c r="O222" t="inlineStr"/>
-      <c r="P222" t="inlineStr"/>
-      <c r="Q222" t="inlineStr"/>
-      <c r="R222" t="inlineStr"/>
+      <c r="P222" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="Q222" t="inlineStr">
+        <is>
+          <t>Ninguna, entendió correctamente</t>
+        </is>
+      </c>
+      <c r="R222" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
       <c r="S222" t="inlineStr"/>
       <c r="T222" t="inlineStr">
         <is>
@@ -21712,7 +21712,7 @@
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>No tiene tiempo para capacitarse</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E232" t="inlineStr">
@@ -21722,17 +21722,17 @@
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>C001475804</t>
+          <t>C001487761</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>C001475804 - PISFIL SIMPALO PETRONILA MARGARITA</t>
+          <t>C001487761 - TORRES HEREDIA ENNA ROXANA</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="I232" s="2" t="n">
@@ -21745,7 +21745,7 @@
       </c>
       <c r="K232" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="L232" t="inlineStr">
@@ -21756,9 +21756,21 @@
       <c r="M232" t="inlineStr"/>
       <c r="N232" t="inlineStr"/>
       <c r="O232" t="inlineStr"/>
-      <c r="P232" t="inlineStr"/>
-      <c r="Q232" t="inlineStr"/>
-      <c r="R232" t="inlineStr"/>
+      <c r="P232" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="Q232" t="inlineStr">
+        <is>
+          <t>Ninguna, entendió correctamente</t>
+        </is>
+      </c>
+      <c r="R232" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
       <c r="S232" t="inlineStr"/>
       <c r="T232" t="inlineStr">
         <is>
@@ -21767,12 +21779,12 @@
       </c>
       <c r="U232" t="inlineStr">
         <is>
-          <t>Nitro</t>
+          <t>Cliente</t>
         </is>
       </c>
       <c r="V232" t="inlineStr">
         <is>
-          <t>SI - Solo tiene pedido por Nitro</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -21794,7 +21806,7 @@
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>No tiene tiempo para capacitarse</t>
         </is>
       </c>
       <c r="E233" t="inlineStr">
@@ -21804,17 +21816,17 @@
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>C001414604</t>
+          <t>C001475804</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>C001414604 - VASQUEZ RAMIREZ YENY CARINA</t>
+          <t>C001475804 - PISFIL SIMPALO PETRONILA MARGARITA</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="I233" s="2" t="n">
@@ -21827,7 +21839,7 @@
       </c>
       <c r="K233" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="L233" t="inlineStr">
@@ -21835,28 +21847,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M233" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
+      <c r="M233" t="inlineStr"/>
       <c r="N233" t="inlineStr"/>
       <c r="O233" t="inlineStr"/>
-      <c r="P233" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="Q233" t="inlineStr">
-        <is>
-          <t>Ninguna, entendió correctamente</t>
-        </is>
-      </c>
-      <c r="R233" t="inlineStr">
-        <is>
-          <t>Mejores promociones</t>
-        </is>
-      </c>
+      <c r="P233" t="inlineStr"/>
+      <c r="Q233" t="inlineStr"/>
+      <c r="R233" t="inlineStr"/>
       <c r="S233" t="inlineStr"/>
       <c r="T233" t="inlineStr">
         <is>
@@ -21865,12 +21861,12 @@
       </c>
       <c r="U233" t="inlineStr">
         <is>
-          <t>Cliente</t>
+          <t>Nitro</t>
         </is>
       </c>
       <c r="V233" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>SI - Solo tiene pedido por Nitro</t>
         </is>
       </c>
     </row>
@@ -21902,12 +21898,12 @@
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>C001487761</t>
+          <t>C001414604</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>C001487761 - TORRES HEREDIA ENNA ROXANA</t>
+          <t>C001414604 - VASQUEZ RAMIREZ YENY CARINA</t>
         </is>
       </c>
       <c r="H234" t="inlineStr">
@@ -21933,7 +21929,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M234" t="inlineStr"/>
+      <c r="M234" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
       <c r="N234" t="inlineStr"/>
       <c r="O234" t="inlineStr"/>
       <c r="P234" t="inlineStr">

--- a/excel/pardadex_capacitaciones.xlsx
+++ b/excel/pardadex_capacitaciones.xlsx
@@ -598,12 +598,12 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>C001697142</t>
+          <t>C001762305</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>C001697142 - CASTANEDA BARON MARIA IVETTE</t>
+          <t>C001762305 - DIAZ DE MECHAN MARIA VIOLETA</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -654,13 +654,17 @@
       <c r="S2" t="inlineStr"/>
       <c r="T2" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -672,7 +676,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>1000049464</t>
+          <t>1000009104</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -692,12 +696,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>C001762305</t>
+          <t>C001739487</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>C001762305 - DIAZ DE MECHAN MARIA VIOLETA</t>
+          <t>C001739487 - CABRERA HUERTAS PENELOPE PASCUALA</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -742,23 +746,19 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Más confianza en la entrega</t>
         </is>
       </c>
       <c r="S3" t="inlineStr"/>
       <c r="T3" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>Cliente</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr"/>
       <c r="V3" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>NO - No hizo pedido</t>
         </is>
       </c>
     </row>
@@ -770,7 +770,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>1000009104</t>
+          <t>1000049464</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -790,12 +790,12 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>C001739487</t>
+          <t>C001684994</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>C001739487 - CABRERA HUERTAS PENELOPE PASCUALA</t>
+          <t>C001684994 - QUIROZ GUTIERREZ PATRICIA LILIANA</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -821,11 +821,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
@@ -840,7 +836,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>Más confianza en la entrega</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
       <c r="S4" t="inlineStr"/>
@@ -874,7 +870,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>No tiene tiempo para capacitarse</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -884,17 +880,17 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>C004172560</t>
+          <t>C001697142</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>C004172560 - LLONTOP SALAZAR MILAGROS DEL PILAR</t>
+          <t>C001697142 - CASTANEDA BARON MARIA IVETTE</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="I5" s="2" t="n">
@@ -907,7 +903,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -915,12 +911,28 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
-      <c r="P5" t="inlineStr"/>
-      <c r="Q5" t="inlineStr"/>
-      <c r="R5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>Ninguna, entendió correctamente</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
       <c r="S5" t="inlineStr"/>
       <c r="T5" t="inlineStr">
         <is>
@@ -952,7 +964,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>No tiene tiempo para capacitarse</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -962,17 +974,17 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>C001684994</t>
+          <t>C004172560</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>C001684994 - QUIROZ GUTIERREZ PATRICIA LILIANA</t>
+          <t>C004172560 - LLONTOP SALAZAR MILAGROS DEL PILAR</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="I6" s="2" t="n">
@@ -985,7 +997,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -996,21 +1008,9 @@
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>Ninguna, entendió correctamente</t>
-        </is>
-      </c>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t>Mejores promociones</t>
-        </is>
-      </c>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr"/>
       <c r="S6" t="inlineStr"/>
       <c r="T6" t="inlineStr">
         <is>
@@ -1232,12 +1232,12 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>C001361114</t>
+          <t>C001078661</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>C001361114 - BARBOZA DE ACUÑA MARIA VIDALA</t>
+          <t>C001078661 - TIMANA BECERRA NANCI</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>1000009104</t>
+          <t>1000049464</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1330,12 +1330,12 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>C001378688</t>
+          <t>C001078670</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>C001378688 - OLIVERA PIEDRA MARIA NELIDA</t>
+          <t>C001078670 - GONZALES GONZALES MARIA FRANCISCA</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1361,11 +1361,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
+      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
@@ -1428,12 +1424,12 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>C001378988</t>
+          <t>C001082584</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>C001378988 - MORI CAPITAN TERESA</t>
+          <t>C001082584 - VASQUEZ CADENILLAS LUZMILA</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1459,11 +1455,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
+      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
@@ -1484,13 +1476,17 @@
       <c r="S11" t="inlineStr"/>
       <c r="T11" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -1522,12 +1518,12 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>C001403645</t>
+          <t>C001084161</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>C001403645 - SILVA TARRILLO MIRIAM ZOILA</t>
+          <t>C001084161 - ARRASCUE MUÑOZ ARIACELI</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1578,13 +1574,17 @@
       <c r="S12" t="inlineStr"/>
       <c r="T12" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -1616,12 +1616,12 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>C001402282</t>
+          <t>C001165739</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>C001402282 - MATEO MORETO CLORINDA</t>
+          <t>C001165739 - DIAZ SILVA EDELMIRA</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1649,7 +1649,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
@@ -1672,17 +1672,13 @@
       <c r="S13" t="inlineStr"/>
       <c r="T13" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U13" t="inlineStr">
-        <is>
-          <t>Cliente</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr"/>
       <c r="V13" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>NO - No hizo pedido</t>
         </is>
       </c>
     </row>
@@ -1714,12 +1710,12 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>C001165739</t>
+          <t>C001361114</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>C001165739 - DIAZ SILVA EDELMIRA</t>
+          <t>C001361114 - BARBOZA DE ACUÑA MARIA VIDALA</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1747,7 +1743,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
@@ -1770,13 +1766,17 @@
       <c r="S14" t="inlineStr"/>
       <c r="T14" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U14" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -1788,7 +1788,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>1000049464</t>
+          <t>1000009104</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1808,12 +1808,12 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>C001078661</t>
+          <t>C001378688</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>C001078661 - TIMANA BECERRA NANCI</t>
+          <t>C001378688 - OLIVERA PIEDRA MARIA NELIDA</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>C001078670</t>
+          <t>C001378988</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>C001078670 - GONZALES GONZALES MARIA FRANCISCA</t>
+          <t>C001378988 - MORI CAPITAN TERESA</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1937,7 +1937,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
@@ -1958,17 +1962,13 @@
       <c r="S16" t="inlineStr"/>
       <c r="T16" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U16" t="inlineStr">
-        <is>
-          <t>Cliente</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr"/>
       <c r="V16" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>NO - No hizo pedido</t>
         </is>
       </c>
     </row>
@@ -2000,12 +2000,12 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>C001082584</t>
+          <t>C001696242</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>C001082584 - VASQUEZ CADENILLAS LUZMILA</t>
+          <t>C001696242 - MARCHENA GONZA NELIDA</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2031,7 +2031,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
       <c r="N17" t="inlineStr"/>
       <c r="O17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
@@ -2094,12 +2098,12 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>C001084161</t>
+          <t>C001573433</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>C001084161 - ARRASCUE MUÑOZ ARIACELI</t>
+          <t>C001573433 - TORRES DELGADO PAOLA MARIANELLA</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2125,11 +2129,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
+      <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="O18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
@@ -2274,12 +2274,12 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>C001541837</t>
+          <t>C001403645</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>C001541837 - DELGADO DE OJEDA ESPERANZA</t>
+          <t>C001403645 - SILVA TARRILLO MIRIAM ZOILA</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2307,7 +2307,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="N20" t="inlineStr"/>
@@ -2330,17 +2330,13 @@
       <c r="S20" t="inlineStr"/>
       <c r="T20" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U20" t="inlineStr">
-        <is>
-          <t>Cliente</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr"/>
       <c r="V20" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>NO - No hizo pedido</t>
         </is>
       </c>
     </row>
@@ -2372,12 +2368,12 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>C001518360</t>
+          <t>C001402282</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>C001518360 - GONZALEZ GONZALEZ MARIA JUANA</t>
+          <t>C001402282 - MATEO MORETO CLORINDA</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2405,7 +2401,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="N21" t="inlineStr"/>
@@ -2470,12 +2466,12 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>C001518368</t>
+          <t>C001541837</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>C001518368 - MIRANDA ARRASCUE MARIA ELIZABETH</t>
+          <t>C001541837 - DELGADO DE OJEDA ESPERANZA</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2503,7 +2499,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="N22" t="inlineStr"/>
@@ -2568,12 +2564,12 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>C001573433</t>
+          <t>C001518360</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>C001573433 - TORRES DELGADO PAOLA MARIANELLA</t>
+          <t>C001518360 - GONZALEZ GONZALEZ MARIA JUANA</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2599,7 +2595,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
       <c r="N23" t="inlineStr"/>
       <c r="O23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
@@ -2642,7 +2642,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>1000009104</t>
+          <t>1000049464</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -2662,12 +2662,12 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>C004165100</t>
+          <t>C001518368</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>C004165100 - VILLARREAL SANTAMARIA ROLANDO FELIX</t>
+          <t>C001518368 - MIRANDA ARRASCUE MARIA ELIZABETH</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -2693,7 +2693,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
       <c r="N24" t="inlineStr"/>
       <c r="O24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
@@ -2736,7 +2740,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>1000049464</t>
+          <t>1000009104</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -2756,12 +2760,12 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>C004097806</t>
+          <t>C004165100</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>C004097806 - HERNANDEZ FLORES WILDOR</t>
+          <t>C004165100 - VILLARREAL SANTAMARIA ROLANDO FELIX</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -2808,13 +2812,17 @@
       <c r="S25" t="inlineStr"/>
       <c r="T25" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U25" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -2846,12 +2854,12 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>C001733892</t>
+          <t>C004097806</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>C001733892 - LEYVA MELENDEZ JORGE LUIS</t>
+          <t>C004097806 - HERNANDEZ FLORES WILDOR</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2898,17 +2906,13 @@
       <c r="S26" t="inlineStr"/>
       <c r="T26" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U26" t="inlineStr">
-        <is>
-          <t>Cliente</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr"/>
       <c r="V26" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>NO - No hizo pedido</t>
         </is>
       </c>
     </row>
@@ -2940,12 +2944,12 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>C001726026</t>
+          <t>C001733892</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>C001726026 - CHAVEZ CHAVEZ MARISOL</t>
+          <t>C001733892 - LEYVA MELENDEZ JORGE LUIS</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2971,11 +2975,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
+      <c r="M27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="O27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
@@ -2996,13 +2996,17 @@
       <c r="S27" t="inlineStr"/>
       <c r="T27" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U27" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -3034,12 +3038,12 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>C001696242</t>
+          <t>C001726026</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>C001696242 - MARCHENA GONZA NELIDA</t>
+          <t>C001726026 - CHAVEZ CHAVEZ MARISOL</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -3067,7 +3071,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="N28" t="inlineStr"/>
@@ -3090,17 +3094,13 @@
       <c r="S28" t="inlineStr"/>
       <c r="T28" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U28" t="inlineStr">
-        <is>
-          <t>Cliente</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr"/>
       <c r="V28" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>NO - No hizo pedido</t>
         </is>
       </c>
     </row>
@@ -3226,12 +3226,12 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>C001654507</t>
+          <t>C001620923</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>C001654507 - CHAPOÑAN CHAPOÑAN MARIA ISABEL</t>
+          <t>C001620923 - FERNANDEZ HERNANDEZ ERICK IGOR</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -3259,7 +3259,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="N30" t="inlineStr"/>
@@ -3310,7 +3310,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>No tiene tiempo para capacitarse</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -3320,17 +3320,17 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>C001620923</t>
+          <t>C001570557</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>C001620923 - FERNANDEZ HERNANDEZ ERICK IGOR</t>
+          <t>C001570557 - SANTISTEBAN ACOSTA SEBASTIAN</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="I31" s="2" t="n">
@@ -3343,7 +3343,7 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -3358,21 +3358,9 @@
       </c>
       <c r="N31" t="inlineStr"/>
       <c r="O31" t="inlineStr"/>
-      <c r="P31" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="Q31" t="inlineStr">
-        <is>
-          <t>Ninguna, entendió correctamente</t>
-        </is>
-      </c>
-      <c r="R31" t="inlineStr">
-        <is>
-          <t>Mejores promociones</t>
-        </is>
-      </c>
+      <c r="P31" t="inlineStr"/>
+      <c r="Q31" t="inlineStr"/>
+      <c r="R31" t="inlineStr"/>
       <c r="S31" t="inlineStr"/>
       <c r="T31" t="inlineStr">
         <is>
@@ -3502,7 +3490,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>No tiene tiempo para capacitarse</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -3512,17 +3500,17 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>C001570557</t>
+          <t>C001654507</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>C001570557 - SANTISTEBAN ACOSTA SEBASTIAN</t>
+          <t>C001654507 - CHAPOÑAN CHAPOÑAN MARIA ISABEL</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="I33" s="2" t="n">
@@ -3535,7 +3523,7 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -3545,14 +3533,26 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="N33" t="inlineStr"/>
       <c r="O33" t="inlineStr"/>
-      <c r="P33" t="inlineStr"/>
-      <c r="Q33" t="inlineStr"/>
-      <c r="R33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>Ninguna, entendió correctamente</t>
+        </is>
+      </c>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
       <c r="S33" t="inlineStr"/>
       <c r="T33" t="inlineStr">
         <is>
@@ -3766,7 +3766,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>1000009104</t>
+          <t>1000049464</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -3786,12 +3786,12 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>C001733879</t>
+          <t>C001753329</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>C001733879 - RODRIGUEZ BALCAZAR GINA OLENKA</t>
+          <t>C001753329 - VILLALOBOS PEREZ DEISY</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -3819,7 +3819,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="N36" t="inlineStr"/>
@@ -3836,23 +3836,19 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>Más productos disponibles</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
       <c r="S36" t="inlineStr"/>
       <c r="T36" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U36" t="inlineStr">
-        <is>
-          <t>Cliente</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr"/>
       <c r="V36" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>NO - No hizo pedido</t>
         </is>
       </c>
     </row>
@@ -4170,12 +4166,12 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>C001726771</t>
+          <t>C001747786</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>C001726771 - ARTEAGA GIL GIANELLA BRIGITTE</t>
+          <t>C001747786 - SILVA ALVARADO ERESBITA ARACELI</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -4201,7 +4197,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
       <c r="N40" t="inlineStr"/>
       <c r="O40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
@@ -4244,7 +4244,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>1000049464</t>
+          <t>1000009104</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -4264,12 +4264,12 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>C001753329</t>
+          <t>C001733879</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>C001753329 - VILLALOBOS PEREZ DEISY</t>
+          <t>C001733879 - RODRIGUEZ BALCAZAR GINA OLENKA</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -4297,7 +4297,7 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="N41" t="inlineStr"/>
@@ -4314,19 +4314,23 @@
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Más productos disponibles</t>
         </is>
       </c>
       <c r="S41" t="inlineStr"/>
       <c r="T41" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U41" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
       <c r="V41" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -4358,12 +4362,12 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>C001747786</t>
+          <t>C001726771</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>C001747786 - SILVA ALVARADO ERESBITA ARACELI</t>
+          <t>C001726771 - ARTEAGA GIL GIANELLA BRIGITTE</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -4389,11 +4393,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
+      <c r="M42" t="inlineStr"/>
       <c r="N42" t="inlineStr"/>
       <c r="O42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
@@ -4436,7 +4436,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>1000009104</t>
+          <t>1000049464</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -4456,12 +4456,12 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>C001507751</t>
+          <t>C001078756</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>C001507751 - MANAY SALAZAR MARIA DEL CARMEN</t>
+          <t>C001078756 - TARRILLO MEJIA ALEX JAVIER</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -4487,7 +4487,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
       <c r="N43" t="inlineStr"/>
       <c r="O43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
@@ -4513,12 +4517,12 @@
       </c>
       <c r="U43" t="inlineStr">
         <is>
-          <t>Cliente</t>
+          <t>Nitro</t>
         </is>
       </c>
       <c r="V43" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>SI - Solo tiene pedido por Nitro</t>
         </is>
       </c>
     </row>
@@ -4530,7 +4534,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>1000049464</t>
+          <t>1000009104</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -4540,7 +4544,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>No tiene tiempo para capacitarse</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -4550,17 +4554,17 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>C001550336</t>
+          <t>C001377892</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>C001550336 - RODAS SANCHEZ CARMEN MERLY</t>
+          <t>C001377892 - CUBAS SANCHEZ SILVIA JANET</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="I44" s="2" t="n">
@@ -4573,7 +4577,7 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
@@ -4584,21 +4588,9 @@
       <c r="M44" t="inlineStr"/>
       <c r="N44" t="inlineStr"/>
       <c r="O44" t="inlineStr"/>
-      <c r="P44" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="Q44" t="inlineStr">
-        <is>
-          <t>Ninguna, entendió correctamente</t>
-        </is>
-      </c>
-      <c r="R44" t="inlineStr">
-        <is>
-          <t>Mejores promociones</t>
-        </is>
-      </c>
+      <c r="P44" t="inlineStr"/>
+      <c r="Q44" t="inlineStr"/>
+      <c r="R44" t="inlineStr"/>
       <c r="S44" t="inlineStr"/>
       <c r="T44" t="inlineStr">
         <is>
@@ -4620,7 +4612,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>1000049464</t>
+          <t>1000009104</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -4640,12 +4632,12 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>C001691214</t>
+          <t>C001656801</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>C001691214 - SANCHEZ TEJADA DORIS</t>
+          <t>C001656801 - ZULOETA ZULOETA HENRY</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -4671,11 +4663,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
+      <c r="M45" t="inlineStr"/>
       <c r="N45" t="inlineStr"/>
       <c r="O45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
@@ -4696,17 +4684,13 @@
       <c r="S45" t="inlineStr"/>
       <c r="T45" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U45" t="inlineStr">
-        <is>
-          <t>Nitro</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr"/>
       <c r="V45" t="inlineStr">
         <is>
-          <t>SI - Solo tiene pedido por Nitro</t>
+          <t>NO - No hizo pedido</t>
         </is>
       </c>
     </row>
@@ -4738,12 +4722,12 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>C001656801</t>
+          <t>C001507751</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>C001656801 - ZULOETA ZULOETA HENRY</t>
+          <t>C001507751 - MANAY SALAZAR MARIA DEL CARMEN</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -4790,13 +4774,17 @@
       <c r="S46" t="inlineStr"/>
       <c r="T46" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U46" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
       <c r="V46" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -4808,7 +4796,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>1000009104</t>
+          <t>1000049464</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -4818,7 +4806,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>No tiene tiempo para capacitarse</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -4828,17 +4816,17 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>C001707748</t>
+          <t>C001550336</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>C001707748 - ESTELA GAMARRA PERCY</t>
+          <t>C001550336 - RODAS SANCHEZ CARMEN MERLY</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="I47" s="2" t="n">
@@ -4851,7 +4839,7 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
@@ -4862,23 +4850,31 @@
       <c r="M47" t="inlineStr"/>
       <c r="N47" t="inlineStr"/>
       <c r="O47" t="inlineStr"/>
-      <c r="P47" t="inlineStr"/>
-      <c r="Q47" t="inlineStr"/>
-      <c r="R47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>Ninguna, entendió correctamente</t>
+        </is>
+      </c>
+      <c r="R47" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
       <c r="S47" t="inlineStr"/>
       <c r="T47" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U47" t="inlineStr">
-        <is>
-          <t>Cliente</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr"/>
       <c r="V47" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>NO - No hizo pedido</t>
         </is>
       </c>
     </row>
@@ -4910,12 +4906,12 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>C001078756</t>
+          <t>C001691214</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>C001078756 - TARRILLO MEJIA ALEX JAVIER</t>
+          <t>C001691214 - SANCHEZ TEJADA DORIS</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -5008,12 +5004,12 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>C001377892</t>
+          <t>C001707748</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>C001377892 - CUBAS SANCHEZ SILVIA JANET</t>
+          <t>C001707748 - ESTELA GAMARRA PERCY</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -5048,13 +5044,17 @@
       <c r="S49" t="inlineStr"/>
       <c r="T49" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U49" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
       <c r="V49" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -5066,7 +5066,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>1000009104</t>
+          <t>1000049464</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -5076,7 +5076,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>No tiene tiempo para capacitarse</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -5086,17 +5086,17 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>C004222016</t>
+          <t>C004175937</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>C004222016 - MEJIA MESTANZA SHAROL LICETH</t>
+          <t>C004175937 - DUAREZ DELGADO CRISTOBAL</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="I50" s="2" t="n">
@@ -5109,7 +5109,7 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
@@ -5124,21 +5124,9 @@
       </c>
       <c r="N50" t="inlineStr"/>
       <c r="O50" t="inlineStr"/>
-      <c r="P50" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="Q50" t="inlineStr">
-        <is>
-          <t>Ninguna, entendió correctamente</t>
-        </is>
-      </c>
-      <c r="R50" t="inlineStr">
-        <is>
-          <t>Mejores promociones</t>
-        </is>
-      </c>
+      <c r="P50" t="inlineStr"/>
+      <c r="Q50" t="inlineStr"/>
+      <c r="R50" t="inlineStr"/>
       <c r="S50" t="inlineStr"/>
       <c r="T50" t="inlineStr">
         <is>
@@ -5268,7 +5256,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>No tiene tiempo para capacitarse</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -5278,17 +5266,17 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>C004160544</t>
+          <t>C004047923</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>C004160544 - SALAZAR DE GONZALES PAULITA</t>
+          <t>C004047923 - HERRERA BALLENA JACKELINE DEL PILAR</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="I52" s="2" t="n">
@@ -5301,7 +5289,7 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
@@ -5316,35 +5304,19 @@
       </c>
       <c r="N52" t="inlineStr"/>
       <c r="O52" t="inlineStr"/>
-      <c r="P52" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="Q52" t="inlineStr">
-        <is>
-          <t>Ninguna, entendió correctamente</t>
-        </is>
-      </c>
-      <c r="R52" t="inlineStr">
-        <is>
-          <t>Mejores promociones</t>
-        </is>
-      </c>
+      <c r="P52" t="inlineStr"/>
+      <c r="Q52" t="inlineStr"/>
+      <c r="R52" t="inlineStr"/>
       <c r="S52" t="inlineStr"/>
       <c r="T52" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U52" t="inlineStr">
-        <is>
-          <t>Cliente</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr"/>
       <c r="V52" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>NO - No hizo pedido</t>
         </is>
       </c>
     </row>
@@ -5376,12 +5348,12 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>C004161330</t>
+          <t>C004160544</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>C004161330 - FERNANDEZ ARCELA MILITZA JERSSUNNY</t>
+          <t>C004160544 - SALAZAR DE GONZALES PAULITA</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -5407,7 +5379,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
       <c r="N53" t="inlineStr"/>
       <c r="O53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
@@ -5460,7 +5436,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>No tiene tiempo para capacitarse</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -5470,17 +5446,17 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>C004175937</t>
+          <t>C004161330</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>C004175937 - DUAREZ DELGADO CRISTOBAL</t>
+          <t>C004161330 - FERNANDEZ ARCELA MILITZA JERSSUNNY</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="I54" s="2" t="n">
@@ -5493,7 +5469,7 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
@@ -5501,16 +5477,24 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
+      <c r="M54" t="inlineStr"/>
       <c r="N54" t="inlineStr"/>
       <c r="O54" t="inlineStr"/>
-      <c r="P54" t="inlineStr"/>
-      <c r="Q54" t="inlineStr"/>
-      <c r="R54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>Ninguna, entendió correctamente</t>
+        </is>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
       <c r="S54" t="inlineStr"/>
       <c r="T54" t="inlineStr">
         <is>
@@ -5536,7 +5520,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>1000049464</t>
+          <t>1000009104</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -5546,7 +5530,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>No tiene tiempo para capacitarse</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -5556,17 +5540,17 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>C004047923</t>
+          <t>C004240567</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>C004047923 - HERRERA BALLENA JACKELINE DEL PILAR</t>
+          <t>C004240567 - DIAZ MEDINA MARIA NELLY</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="I55" s="2" t="n">
@@ -5579,7 +5563,7 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
@@ -5587,26 +5571,38 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
+      <c r="M55" t="inlineStr"/>
       <c r="N55" t="inlineStr"/>
       <c r="O55" t="inlineStr"/>
-      <c r="P55" t="inlineStr"/>
-      <c r="Q55" t="inlineStr"/>
-      <c r="R55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>Ninguna, entendió correctamente</t>
+        </is>
+      </c>
+      <c r="R55" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
       <c r="S55" t="inlineStr"/>
       <c r="T55" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U55" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Nitro</t>
+        </is>
+      </c>
       <c r="V55" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Solo tiene pedido por Nitro</t>
         </is>
       </c>
     </row>
@@ -5638,12 +5634,12 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>C001549310</t>
+          <t>C004222016</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>C001549310 - BENAVIDES SAAVEDRA MARITA GUISELA</t>
+          <t>C004222016 - MEJIA MESTANZA SHAROL LICETH</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -5669,7 +5665,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
       <c r="N56" t="inlineStr"/>
       <c r="O56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
@@ -5690,13 +5690,17 @@
       <c r="S56" t="inlineStr"/>
       <c r="T56" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U56" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
       <c r="V56" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -5822,12 +5826,12 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>C004240567</t>
+          <t>C001549310</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>C004240567 - DIAZ MEDINA MARIA NELLY</t>
+          <t>C001549310 - BENAVIDES SAAVEDRA MARITA GUISELA</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -5874,17 +5878,13 @@
       <c r="S58" t="inlineStr"/>
       <c r="T58" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U58" t="inlineStr">
-        <is>
-          <t>Nitro</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr"/>
       <c r="V58" t="inlineStr">
         <is>
-          <t>SI - Solo tiene pedido por Nitro</t>
+          <t>NO - No hizo pedido</t>
         </is>
       </c>
     </row>
@@ -5906,7 +5906,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>No tiene tiempo para capacitarse</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -5916,17 +5916,17 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>C004166743</t>
+          <t>C001165908</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>C004166743 - LLAMOSA ORMEÑO ORLANDO</t>
+          <t>C001165908 - BANCES ENEQUE LADY MARIBEL</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="I59" s="2" t="n">
@@ -5939,7 +5939,7 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
@@ -5947,22 +5947,42 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
       <c r="N59" t="inlineStr"/>
       <c r="O59" t="inlineStr"/>
-      <c r="P59" t="inlineStr"/>
-      <c r="Q59" t="inlineStr"/>
-      <c r="R59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="Q59" t="inlineStr">
+        <is>
+          <t>Ninguna, entendió correctamente</t>
+        </is>
+      </c>
+      <c r="R59" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
       <c r="S59" t="inlineStr"/>
       <c r="T59" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U59" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
       <c r="V59" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -5994,12 +6014,12 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>C001717998</t>
+          <t>C001165821</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>C001717998 - MONTEZA FERNANDEZ MEDALI TEODOSIA</t>
+          <t>C001165821 - ALDUI GASTELO INES</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -6027,7 +6047,7 @@
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="N60" t="inlineStr"/>
@@ -6050,13 +6070,17 @@
       <c r="S60" t="inlineStr"/>
       <c r="T60" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U60" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
       <c r="V60" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -6068,7 +6092,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>1000049464</t>
+          <t>1000009104</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -6088,12 +6112,12 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>C001165908</t>
+          <t>C001085135</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>C001165908 - BANCES ENEQUE LADY MARIBEL</t>
+          <t>C001085135 - GUEVARA DE MANOSALVA MARIA TEONILA</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -6119,11 +6143,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
+      <c r="M61" t="inlineStr"/>
       <c r="N61" t="inlineStr"/>
       <c r="O61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
@@ -6166,7 +6186,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>1000049464</t>
+          <t>1000009104</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -6186,12 +6206,12 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>C001165821</t>
+          <t>C001082245</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>C001165821 - ALDUI GASTELO INES</t>
+          <t>C001082245 - MECHAN TORRES JUANA</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -6219,7 +6239,7 @@
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="N62" t="inlineStr"/>
@@ -6247,12 +6267,12 @@
       </c>
       <c r="U62" t="inlineStr">
         <is>
-          <t>Cliente</t>
+          <t>Nitro</t>
         </is>
       </c>
       <c r="V62" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>SI - Solo tiene pedido por Nitro</t>
         </is>
       </c>
     </row>
@@ -6942,12 +6962,12 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>C004240340</t>
+          <t>C001717998</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>C004240340 - RACHI TABOADA MAGDALENA</t>
+          <t>C001717998 - MONTEZA FERNANDEZ MEDALI TEODOSIA</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -6973,7 +6993,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
       <c r="N70" t="inlineStr"/>
       <c r="O70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
@@ -7022,7 +7046,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>No tiene tiempo para capacitarse</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -7032,17 +7056,17 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>C004240362</t>
+          <t>C004166743</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>C004240362 - ALVAREZ SORIANO SILVIA PAOLA</t>
+          <t>C004166743 - LLAMOSA ORMEÑO ORLANDO</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="I71" s="2" t="n">
@@ -7055,7 +7079,7 @@
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
@@ -7066,35 +7090,19 @@
       <c r="M71" t="inlineStr"/>
       <c r="N71" t="inlineStr"/>
       <c r="O71" t="inlineStr"/>
-      <c r="P71" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="Q71" t="inlineStr">
-        <is>
-          <t>Ninguna, entendió correctamente</t>
-        </is>
-      </c>
-      <c r="R71" t="inlineStr">
-        <is>
-          <t>Mejores promociones</t>
-        </is>
-      </c>
+      <c r="P71" t="inlineStr"/>
+      <c r="Q71" t="inlineStr"/>
+      <c r="R71" t="inlineStr"/>
       <c r="S71" t="inlineStr"/>
       <c r="T71" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U71" t="inlineStr">
-        <is>
-          <t>Cliente</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr"/>
       <c r="V71" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>NO - No hizo pedido</t>
         </is>
       </c>
     </row>
@@ -7116,7 +7124,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>No tiene tiempo para capacitarse</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -7126,17 +7134,17 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>C004166024</t>
+          <t>C004240340</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>C004166024 - SANTISTEBAN DE TINOCO EMMA</t>
+          <t>C004240340 - RACHI TABOADA MAGDALENA</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="I72" s="2" t="n">
@@ -7149,7 +7157,7 @@
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
@@ -7160,23 +7168,31 @@
       <c r="M72" t="inlineStr"/>
       <c r="N72" t="inlineStr"/>
       <c r="O72" t="inlineStr"/>
-      <c r="P72" t="inlineStr"/>
-      <c r="Q72" t="inlineStr"/>
-      <c r="R72" t="inlineStr"/>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="Q72" t="inlineStr">
+        <is>
+          <t>Ninguna, entendió correctamente</t>
+        </is>
+      </c>
+      <c r="R72" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
       <c r="S72" t="inlineStr"/>
       <c r="T72" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U72" t="inlineStr">
-        <is>
-          <t>Cliente</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr"/>
       <c r="V72" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>NO - No hizo pedido</t>
         </is>
       </c>
     </row>
@@ -7208,12 +7224,12 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>C004166739</t>
+          <t>C004240362</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>C004166739 - SANTISTEBAN ACOSTA CARMEN ROSA</t>
+          <t>C004240362 - ALVAREZ SORIANO SILVIA PAOLA</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -7302,12 +7318,12 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>C004167751</t>
+          <t>C001414604</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>C004167751 - MEZA CALDERON LUIS HENRY</t>
+          <t>C001414604 - VASQUEZ RAMIREZ YENY CARINA</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -7386,7 +7402,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>No tiene tiempo para capacitarse</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -7396,17 +7412,17 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>C004094224</t>
+          <t>C001487318</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>C004094224 - QUIROZ SANTISTEBAN KATHERIN DEL MILAGRO</t>
+          <t>C001487318 - HUACCHILLO VEGA DAISY</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="I75" s="2" t="n">
@@ -7419,7 +7435,7 @@
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
@@ -7429,24 +7445,40 @@
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="N75" t="inlineStr"/>
       <c r="O75" t="inlineStr"/>
-      <c r="P75" t="inlineStr"/>
-      <c r="Q75" t="inlineStr"/>
-      <c r="R75" t="inlineStr"/>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="Q75" t="inlineStr">
+        <is>
+          <t>Ninguna, entendió correctamente</t>
+        </is>
+      </c>
+      <c r="R75" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
       <c r="S75" t="inlineStr"/>
       <c r="T75" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U75" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
       <c r="V75" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -7458,7 +7490,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>1000049464</t>
+          <t>1000009104</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -7478,12 +7510,12 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>C001487318</t>
+          <t>C001077387</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>C001487318 - HUACCHILLO VEGA DAISY</t>
+          <t>C001077387 - CASUSOL DELGADO DE GARCIA ROSA AMELIA</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -7509,11 +7541,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M76" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
+      <c r="M76" t="inlineStr"/>
       <c r="N76" t="inlineStr"/>
       <c r="O76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
@@ -7576,12 +7604,12 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>C001414604</t>
+          <t>C001165828</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>C001414604 - VASQUEZ RAMIREZ YENY CARINA</t>
+          <t>C001165828 - JIMENEZ VALENCIA MARIA GLADYS</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -7607,7 +7635,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M77" t="inlineStr"/>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
       <c r="N77" t="inlineStr"/>
       <c r="O77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
@@ -7633,12 +7665,12 @@
       </c>
       <c r="U77" t="inlineStr">
         <is>
-          <t>Cliente</t>
+          <t>Nitro</t>
         </is>
       </c>
       <c r="V77" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>SI - Solo tiene pedido por Nitro</t>
         </is>
       </c>
     </row>
@@ -7650,7 +7682,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>1000009104</t>
+          <t>1000049464</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -7660,7 +7692,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>No tiene tiempo para capacitarse</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -7670,17 +7702,17 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>C001077387</t>
+          <t>C001703938</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>C001077387 - CASUSOL DELGADO DE GARCIA ROSA AMELIA</t>
+          <t>C001703938 - ALDANA SALAZAR SHEYLA KARINA</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="I78" s="2" t="n">
@@ -7693,7 +7725,7 @@
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
@@ -7701,38 +7733,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M78" t="inlineStr"/>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
       <c r="N78" t="inlineStr"/>
       <c r="O78" t="inlineStr"/>
-      <c r="P78" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="Q78" t="inlineStr">
-        <is>
-          <t>Ninguna, entendió correctamente</t>
-        </is>
-      </c>
-      <c r="R78" t="inlineStr">
-        <is>
-          <t>Mejores promociones</t>
-        </is>
-      </c>
+      <c r="P78" t="inlineStr"/>
+      <c r="Q78" t="inlineStr"/>
+      <c r="R78" t="inlineStr"/>
       <c r="S78" t="inlineStr"/>
       <c r="T78" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U78" t="inlineStr">
-        <is>
-          <t>Cliente</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr"/>
       <c r="V78" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>NO - No hizo pedido</t>
         </is>
       </c>
     </row>
@@ -7764,12 +7784,12 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>C001165828</t>
+          <t>C001751925</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>C001165828 - JIMENEZ VALENCIA MARIA GLADYS</t>
+          <t>C001751925 - KININ TINCHO RAQUELINA</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -7797,7 +7817,7 @@
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="N79" t="inlineStr"/>
@@ -7820,17 +7840,13 @@
       <c r="S79" t="inlineStr"/>
       <c r="T79" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U79" t="inlineStr">
-        <is>
-          <t>Nitro</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr"/>
       <c r="V79" t="inlineStr">
         <is>
-          <t>SI - Solo tiene pedido por Nitro</t>
+          <t>NO - No hizo pedido</t>
         </is>
       </c>
     </row>
@@ -7852,7 +7868,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>No tiene tiempo para capacitarse</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -7862,17 +7878,17 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>C001751925</t>
+          <t>C004094224</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>C001751925 - KININ TINCHO RAQUELINA</t>
+          <t>C004094224 - QUIROZ SANTISTEBAN KATHERIN DEL MILAGRO</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="I80" s="2" t="n">
@@ -7885,7 +7901,7 @@
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
@@ -7900,21 +7916,9 @@
       </c>
       <c r="N80" t="inlineStr"/>
       <c r="O80" t="inlineStr"/>
-      <c r="P80" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="Q80" t="inlineStr">
-        <is>
-          <t>Ninguna, entendió correctamente</t>
-        </is>
-      </c>
-      <c r="R80" t="inlineStr">
-        <is>
-          <t>Mejores promociones</t>
-        </is>
-      </c>
+      <c r="P80" t="inlineStr"/>
+      <c r="Q80" t="inlineStr"/>
+      <c r="R80" t="inlineStr"/>
       <c r="S80" t="inlineStr"/>
       <c r="T80" t="inlineStr">
         <is>
@@ -7956,12 +7960,12 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>C001703938</t>
+          <t>C004166024</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>C001703938 - ALDANA SALAZAR SHEYLA KARINA</t>
+          <t>C004166024 - SANTISTEBAN DE TINOCO EMMA</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -7987,11 +7991,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M81" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
+      <c r="M81" t="inlineStr"/>
       <c r="N81" t="inlineStr"/>
       <c r="O81" t="inlineStr"/>
       <c r="P81" t="inlineStr"/>
@@ -8000,13 +8000,17 @@
       <c r="S81" t="inlineStr"/>
       <c r="T81" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U81" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
       <c r="V81" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -8018,7 +8022,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>1000009104</t>
+          <t>1000049464</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -8038,12 +8042,12 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>C001085135</t>
+          <t>C004166739</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>C001085135 - GUEVARA DE MANOSALVA MARIA TEONILA</t>
+          <t>C004166739 - SANTISTEBAN ACOSTA CARMEN ROSA</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -8112,7 +8116,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>1000009104</t>
+          <t>1000049464</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -8132,12 +8136,12 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>C001082245</t>
+          <t>C004167751</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>C001082245 - MECHAN TORRES JUANA</t>
+          <t>C004167751 - MEZA CALDERON LUIS HENRY</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -8163,11 +8167,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M83" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
+      <c r="M83" t="inlineStr"/>
       <c r="N83" t="inlineStr"/>
       <c r="O83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="U83" t="inlineStr">
         <is>
-          <t>Nitro</t>
+          <t>Cliente</t>
         </is>
       </c>
       <c r="V83" t="inlineStr">
         <is>
-          <t>SI - Solo tiene pedido por Nitro</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -10720,7 +10720,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>1000049464</t>
+          <t>1000009104</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -10740,12 +10740,12 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>C001732282</t>
+          <t>C001733879</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>C001732282 - SANTA CRUZ RENTERIA BETTY NAYELI</t>
+          <t>C001733879 - RODRIGUEZ BALCAZAR GINA OLENKA</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -10801,12 +10801,12 @@
       </c>
       <c r="U111" t="inlineStr">
         <is>
-          <t>Nitro</t>
+          <t>Cliente</t>
         </is>
       </c>
       <c r="V111" t="inlineStr">
         <is>
-          <t>SI - Solo tiene pedido por Nitro</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -10818,7 +10818,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>1000009104</t>
+          <t>1000049464</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -10838,12 +10838,12 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>C001733879</t>
+          <t>C001732282</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>C001733879 - RODRIGUEZ BALCAZAR GINA OLENKA</t>
+          <t>C001732282 - SANTA CRUZ RENTERIA BETTY NAYELI</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -10899,12 +10899,12 @@
       </c>
       <c r="U112" t="inlineStr">
         <is>
-          <t>Cliente</t>
+          <t>Nitro</t>
         </is>
       </c>
       <c r="V112" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>SI - Solo tiene pedido por Nitro</t>
         </is>
       </c>
     </row>
@@ -11226,12 +11226,12 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>C001685898</t>
+          <t>C001503171</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>C001685898 - VALENCIA RODAS DIANA KATHERINE</t>
+          <t>C001503171 - ARRIVASPLATA BECERRA ROSA</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -11266,7 +11266,7 @@
       <c r="O116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
-          <t>Algo dispuesto</t>
+          <t>Muy dispuesto</t>
         </is>
       </c>
       <c r="Q116" t="inlineStr">
@@ -11282,13 +11282,17 @@
       <c r="S116" t="inlineStr"/>
       <c r="T116" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U116" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U116" t="inlineStr">
+        <is>
+          <t>Nitro</t>
+        </is>
+      </c>
       <c r="V116" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Solo tiene pedido por Nitro</t>
         </is>
       </c>
     </row>
@@ -11300,7 +11304,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>1000009104</t>
+          <t>1000049464</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -11320,12 +11324,12 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>C001452822</t>
+          <t>C001685898</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>C001452822 - FERNANDEZ CABRERA LUISA</t>
+          <t>C001685898 - VALENCIA RODAS DIANA KATHERINE</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -11360,7 +11364,7 @@
       <c r="O117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
-          <t>Muy dispuesto</t>
+          <t>Algo dispuesto</t>
         </is>
       </c>
       <c r="Q117" t="inlineStr">
@@ -11376,17 +11380,13 @@
       <c r="S117" t="inlineStr"/>
       <c r="T117" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U117" t="inlineStr">
-        <is>
-          <t>Cliente</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U117" t="inlineStr"/>
       <c r="V117" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>NO - No hizo pedido</t>
         </is>
       </c>
     </row>
@@ -11398,7 +11398,7 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>1000049464</t>
+          <t>1000009104</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -11418,12 +11418,12 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>C001503171</t>
+          <t>C001452822</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>C001503171 - ARRIVASPLATA BECERRA ROSA</t>
+          <t>C001452822 - FERNANDEZ CABRERA LUISA</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -11479,12 +11479,12 @@
       </c>
       <c r="U118" t="inlineStr">
         <is>
-          <t>Nitro</t>
+          <t>Cliente</t>
         </is>
       </c>
       <c r="V118" t="inlineStr">
         <is>
-          <t>SI - Solo tiene pedido por Nitro</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -11708,12 +11708,12 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>C004172041</t>
+          <t>C001733538</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>C004172041 - RAMIREZ PALACIOS ANTONIA ROSALIA</t>
+          <t>C001733538 - FARFAN RELAIZA YTALA</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -11806,12 +11806,12 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>C004172093</t>
+          <t>C004172041</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>C004172093 - ALDANA GARCIA TEODOCIA YSABEL</t>
+          <t>C004172041 - RAMIREZ PALACIOS ANTONIA ROSALIA</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -11904,12 +11904,12 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>C001077720</t>
+          <t>C004172093</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>C001077720 - BRAVO CHOZO TOMAS</t>
+          <t>C004172093 - ALDANA GARCIA TEODOCIA YSABEL</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -11937,7 +11937,7 @@
       </c>
       <c r="M123" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="N123" t="inlineStr"/>
@@ -12002,12 +12002,12 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>C001075708</t>
+          <t>C001077720</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>C001075708 - CUEVA DE ESTRADA GENARA</t>
+          <t>C001077720 - BRAVO CHOZO TOMAS</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -12035,7 +12035,7 @@
       </c>
       <c r="M124" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="N124" t="inlineStr"/>
@@ -12080,7 +12080,7 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>1000009104</t>
+          <t>1000049464</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -12100,12 +12100,12 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>C001474582</t>
+          <t>C001075708</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>C001474582 - MCCUBY MIRANDA ROSA ELENA</t>
+          <t>C001075708 - CUEVA DE ESTRADA GENARA</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -12178,7 +12178,7 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>1000049464</t>
+          <t>1000009104</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -12198,12 +12198,12 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>C001733538</t>
+          <t>C001474582</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>C001733538 - FARFAN RELAIZA YTALA</t>
+          <t>C001474582 - MCCUBY MIRANDA ROSA ELENA</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -13122,7 +13122,7 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>1000049464</t>
+          <t>1000009104</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -13142,12 +13142,12 @@
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>C001751104</t>
+          <t>C004241151</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>C001751104 - REYES CHUMACERO MARCOS ANDERSON</t>
+          <t>C004241151 - TERAN CAYAO MAGALY</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
@@ -13175,19 +13175,19 @@
       </c>
       <c r="M136" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="N136" t="inlineStr"/>
       <c r="O136" t="inlineStr"/>
       <c r="P136" t="inlineStr">
         <is>
-          <t>Algo dispuesto</t>
+          <t>Muy dispuesto</t>
         </is>
       </c>
       <c r="Q136" t="inlineStr">
         <is>
-          <t>Ninguna, entendió correctamente</t>
+          <t>Iniciar sesión</t>
         </is>
       </c>
       <c r="R136" t="inlineStr">
@@ -13203,12 +13203,12 @@
       </c>
       <c r="U136" t="inlineStr">
         <is>
-          <t>Nitro</t>
+          <t>Cliente</t>
         </is>
       </c>
       <c r="V136" t="inlineStr">
         <is>
-          <t>SI - Solo tiene pedido por Nitro</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -13240,12 +13240,12 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>C004047577</t>
+          <t>C004210654</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>C004047577 - CORREA DE CAMPOS CRISTINA</t>
+          <t>C004210654 - CHUGDEN CANCINO WALTER</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -13296,17 +13296,13 @@
       <c r="S137" t="inlineStr"/>
       <c r="T137" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U137" t="inlineStr">
-        <is>
-          <t>Cliente</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U137" t="inlineStr"/>
       <c r="V137" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>NO - No hizo pedido</t>
         </is>
       </c>
     </row>
@@ -13338,12 +13334,12 @@
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>C001761288</t>
+          <t>C004165869</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>C001761288 - DAVILA FLORES LLAMI</t>
+          <t>C004165869 - PLACENCIA LEYTON ANA LAURA</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -13371,7 +13367,7 @@
       </c>
       <c r="M138" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="N138" t="inlineStr"/>
@@ -13416,7 +13412,7 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>1000009104</t>
+          <t>1000049464</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -13436,12 +13432,12 @@
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>C004241151</t>
+          <t>C001751104</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>C004241151 - TERAN CAYAO MAGALY</t>
+          <t>C001751104 - REYES CHUMACERO MARCOS ANDERSON</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
@@ -13469,19 +13465,19 @@
       </c>
       <c r="M139" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="N139" t="inlineStr"/>
       <c r="O139" t="inlineStr"/>
       <c r="P139" t="inlineStr">
         <is>
-          <t>Muy dispuesto</t>
+          <t>Algo dispuesto</t>
         </is>
       </c>
       <c r="Q139" t="inlineStr">
         <is>
-          <t>Iniciar sesión</t>
+          <t>Ninguna, entendió correctamente</t>
         </is>
       </c>
       <c r="R139" t="inlineStr">
@@ -13497,12 +13493,12 @@
       </c>
       <c r="U139" t="inlineStr">
         <is>
-          <t>Cliente</t>
+          <t>Nitro</t>
         </is>
       </c>
       <c r="V139" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>SI - Solo tiene pedido por Nitro</t>
         </is>
       </c>
     </row>
@@ -13534,12 +13530,12 @@
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>C004210654</t>
+          <t>C004047577</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>C004210654 - CHUGDEN CANCINO WALTER</t>
+          <t>C004047577 - CORREA DE CAMPOS CRISTINA</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
@@ -13590,13 +13586,17 @@
       <c r="S140" t="inlineStr"/>
       <c r="T140" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U140" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U140" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
       <c r="V140" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -13628,12 +13628,12 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>C004165869</t>
+          <t>C001761288</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>C004165869 - PLACENCIA LEYTON ANA LAURA</t>
+          <t>C001761288 - DAVILA FLORES LLAMI</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -13661,7 +13661,7 @@
       </c>
       <c r="M141" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="N141" t="inlineStr"/>
@@ -13896,7 +13896,7 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>No tiene tiempo para capacitarse</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
@@ -13906,17 +13906,17 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>C001483403</t>
+          <t>C001165904</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>C001483403 - CALDERON COBA GLADIS</t>
+          <t>C001165904 - VASQUEZ CUBAS MARIA LUCINA</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="I144" s="2" t="n">
@@ -13929,7 +13929,7 @@
       </c>
       <c r="K144" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="L144" t="inlineStr">
@@ -13944,21 +13944,9 @@
       </c>
       <c r="N144" t="inlineStr"/>
       <c r="O144" t="inlineStr"/>
-      <c r="P144" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="Q144" t="inlineStr">
-        <is>
-          <t>Ninguna, entendió correctamente</t>
-        </is>
-      </c>
-      <c r="R144" t="inlineStr">
-        <is>
-          <t>Mejores promociones</t>
-        </is>
-      </c>
+      <c r="P144" t="inlineStr"/>
+      <c r="Q144" t="inlineStr"/>
+      <c r="R144" t="inlineStr"/>
       <c r="S144" t="inlineStr"/>
       <c r="T144" t="inlineStr">
         <is>
@@ -13994,7 +13982,7 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>No tiene tiempo para capacitarse</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
@@ -14004,17 +13992,17 @@
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>C001165904</t>
+          <t>C001483403</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>C001165904 - VASQUEZ CUBAS MARIA LUCINA</t>
+          <t>C001483403 - CALDERON COBA GLADIS</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="I145" s="2" t="n">
@@ -14027,7 +14015,7 @@
       </c>
       <c r="K145" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="L145" t="inlineStr">
@@ -14042,9 +14030,21 @@
       </c>
       <c r="N145" t="inlineStr"/>
       <c r="O145" t="inlineStr"/>
-      <c r="P145" t="inlineStr"/>
-      <c r="Q145" t="inlineStr"/>
-      <c r="R145" t="inlineStr"/>
+      <c r="P145" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="Q145" t="inlineStr">
+        <is>
+          <t>Ninguna, entendió correctamente</t>
+        </is>
+      </c>
+      <c r="R145" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
       <c r="S145" t="inlineStr"/>
       <c r="T145" t="inlineStr">
         <is>
@@ -14576,12 +14576,12 @@
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>C001737386</t>
+          <t>C001734798</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>C001737386 - MONZON ORDINOLA MARITA ESTHER</t>
+          <t>C001734798 - MANAYALLE CABRERA SILVIA ELIANA</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
@@ -14607,7 +14607,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M151" t="inlineStr"/>
+      <c r="M151" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
       <c r="N151" t="inlineStr"/>
       <c r="O151" t="inlineStr"/>
       <c r="P151" t="inlineStr">
@@ -14670,12 +14674,12 @@
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>C001737414</t>
+          <t>C001736067</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>C001737414 - BRIONES DAMIAN LILA DEL CARMEN</t>
+          <t>C001736067 - ANCAJIMA SARRIN JORGE ERICKSON</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
@@ -14701,11 +14705,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M152" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
+      <c r="M152" t="inlineStr"/>
       <c r="N152" t="inlineStr"/>
       <c r="O152" t="inlineStr"/>
       <c r="P152" t="inlineStr">
@@ -14768,12 +14768,12 @@
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>C001734798</t>
+          <t>C001736074</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>C001734798 - MANAYALLE CABRERA SILVIA ELIANA</t>
+          <t>C001736074 - AGIP SALAZAR ROSSANITA</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
@@ -14801,7 +14801,7 @@
       </c>
       <c r="M153" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="N153" t="inlineStr"/>
@@ -14813,7 +14813,7 @@
       </c>
       <c r="Q153" t="inlineStr">
         <is>
-          <t>Ninguna, entendió correctamente</t>
+          <t>Iniciar sesión</t>
         </is>
       </c>
       <c r="R153" t="inlineStr">
@@ -14824,17 +14824,13 @@
       <c r="S153" t="inlineStr"/>
       <c r="T153" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U153" t="inlineStr">
-        <is>
-          <t>Cliente</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U153" t="inlineStr"/>
       <c r="V153" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>NO - No hizo pedido</t>
         </is>
       </c>
     </row>
@@ -14866,12 +14862,12 @@
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>C001736067</t>
+          <t>C001743638</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>C001736067 - ANCAJIMA SARRIN JORGE ERICKSON</t>
+          <t>C001743638 - LLATAS IZQUIERDO YUDI</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
@@ -14897,12 +14893,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M154" t="inlineStr"/>
+      <c r="M154" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
       <c r="N154" t="inlineStr"/>
       <c r="O154" t="inlineStr"/>
       <c r="P154" t="inlineStr">
         <is>
-          <t>Muy dispuesto</t>
+          <t>Algo dispuesto</t>
         </is>
       </c>
       <c r="Q154" t="inlineStr">
@@ -14923,12 +14923,12 @@
       </c>
       <c r="U154" t="inlineStr">
         <is>
-          <t>Cliente</t>
+          <t>Nitro</t>
         </is>
       </c>
       <c r="V154" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>SI - Solo tiene pedido por Nitro</t>
         </is>
       </c>
     </row>
@@ -14960,12 +14960,12 @@
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>C001736074</t>
+          <t>C001737386</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>C001736074 - AGIP SALAZAR ROSSANITA</t>
+          <t>C001737386 - MONZON ORDINOLA MARITA ESTHER</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
@@ -14991,11 +14991,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M155" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
+      <c r="M155" t="inlineStr"/>
       <c r="N155" t="inlineStr"/>
       <c r="O155" t="inlineStr"/>
       <c r="P155" t="inlineStr">
@@ -15005,7 +15001,7 @@
       </c>
       <c r="Q155" t="inlineStr">
         <is>
-          <t>Iniciar sesión</t>
+          <t>Ninguna, entendió correctamente</t>
         </is>
       </c>
       <c r="R155" t="inlineStr">
@@ -15016,13 +15012,17 @@
       <c r="S155" t="inlineStr"/>
       <c r="T155" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U155" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U155" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
       <c r="V155" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -15054,12 +15054,12 @@
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>C001743638</t>
+          <t>C001737414</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>C001743638 - LLATAS IZQUIERDO YUDI</t>
+          <t>C001737414 - BRIONES DAMIAN LILA DEL CARMEN</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
@@ -15094,7 +15094,7 @@
       <c r="O156" t="inlineStr"/>
       <c r="P156" t="inlineStr">
         <is>
-          <t>Algo dispuesto</t>
+          <t>Muy dispuesto</t>
         </is>
       </c>
       <c r="Q156" t="inlineStr">
@@ -15115,12 +15115,12 @@
       </c>
       <c r="U156" t="inlineStr">
         <is>
-          <t>Nitro</t>
+          <t>Cliente</t>
         </is>
       </c>
       <c r="V156" t="inlineStr">
         <is>
-          <t>SI - Solo tiene pedido por Nitro</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -15888,12 +15888,12 @@
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>C001464462</t>
+          <t>C001163238</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>C001464462 - BUENO GALAN ANGELICA MARIA</t>
+          <t>C001163238 - QUEVEDO RAMIREZ ALFREDO</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
@@ -15921,7 +15921,7 @@
       </c>
       <c r="M165" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="N165" t="inlineStr"/>
@@ -15949,12 +15949,12 @@
       </c>
       <c r="U165" t="inlineStr">
         <is>
-          <t>Nitro</t>
+          <t>Cliente</t>
         </is>
       </c>
       <c r="V165" t="inlineStr">
         <is>
-          <t>SI - Solo tiene pedido por Nitro</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -15986,12 +15986,12 @@
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>C001163238</t>
+          <t>C001072350</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>C001163238 - QUEVEDO RAMIREZ ALFREDO</t>
+          <t>C001072350 - PERES SANCHEZ SUSANA FILOMENA</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
@@ -16019,7 +16019,7 @@
       </c>
       <c r="M166" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="N166" t="inlineStr"/>
@@ -16084,12 +16084,12 @@
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>C001072350</t>
+          <t>C001464462</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>C001072350 - PERES SANCHEZ SUSANA FILOMENA</t>
+          <t>C001464462 - BUENO GALAN ANGELICA MARIA</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
@@ -16145,12 +16145,12 @@
       </c>
       <c r="U167" t="inlineStr">
         <is>
-          <t>Cliente</t>
+          <t>Nitro</t>
         </is>
       </c>
       <c r="V167" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>SI - Solo tiene pedido por Nitro</t>
         </is>
       </c>
     </row>
@@ -16562,12 +16562,12 @@
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>C001648256</t>
+          <t>C004177292</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>C001648256 - SUCLUPE BANCES SEGUNDINA</t>
+          <t>C004177292 - SAAVEDRA CASTILLO GLORIA</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
@@ -16598,7 +16598,7 @@
       <c r="O172" t="inlineStr"/>
       <c r="P172" t="inlineStr">
         <is>
-          <t>Muy dispuesto</t>
+          <t>Algo dispuesto</t>
         </is>
       </c>
       <c r="Q172" t="inlineStr">
@@ -16608,7 +16608,7 @@
       </c>
       <c r="R172" t="inlineStr">
         <is>
-          <t>Más confianza en la entrega</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
       <c r="S172" t="inlineStr"/>
@@ -16656,12 +16656,12 @@
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>C001633685</t>
+          <t>C001765640</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>C001633685 - LOZADA PAREDES ROCIVEL LILIANA</t>
+          <t>C001765640 - CATON CORDOVA NURY ADITA</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
@@ -16926,12 +16926,12 @@
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>C004177292</t>
+          <t>C001648256</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>C004177292 - SAAVEDRA CASTILLO GLORIA</t>
+          <t>C001648256 - SUCLUPE BANCES SEGUNDINA</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
@@ -16962,7 +16962,7 @@
       <c r="O176" t="inlineStr"/>
       <c r="P176" t="inlineStr">
         <is>
-          <t>Algo dispuesto</t>
+          <t>Muy dispuesto</t>
         </is>
       </c>
       <c r="Q176" t="inlineStr">
@@ -16972,7 +16972,7 @@
       </c>
       <c r="R176" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Más confianza en la entrega</t>
         </is>
       </c>
       <c r="S176" t="inlineStr"/>
@@ -17020,12 +17020,12 @@
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>C001765640</t>
+          <t>C001633685</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>C001765640 - CATON CORDOVA NURY ADITA</t>
+          <t>C001633685 - LOZADA PAREDES ROCIVEL LILIANA</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
@@ -17468,7 +17468,7 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>No tiene tiempo para capacitarse</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
@@ -17478,17 +17478,17 @@
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>C001696221</t>
+          <t>C001745658</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>C001696221 - VENTURA SUCLUPE MARIA FILOMENA</t>
+          <t>C001745658 - BRAVO PISCOYA MARIA GRIMALDINA</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="I182" s="2" t="n">
@@ -17501,7 +17501,7 @@
       </c>
       <c r="K182" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="L182" t="inlineStr">
@@ -17509,24 +17509,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M182" t="inlineStr"/>
+      <c r="M182" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
       <c r="N182" t="inlineStr"/>
       <c r="O182" t="inlineStr"/>
-      <c r="P182" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="Q182" t="inlineStr">
-        <is>
-          <t>Ninguna, entendió correctamente</t>
-        </is>
-      </c>
-      <c r="R182" t="inlineStr">
-        <is>
-          <t>Mejores promociones</t>
-        </is>
-      </c>
+      <c r="P182" t="inlineStr"/>
+      <c r="Q182" t="inlineStr"/>
+      <c r="R182" t="inlineStr"/>
       <c r="S182" t="inlineStr"/>
       <c r="T182" t="inlineStr">
         <is>
@@ -17562,7 +17554,7 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>No tiene tiempo para capacitarse</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
@@ -17572,17 +17564,17 @@
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>C001745658</t>
+          <t>C001696221</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>C001745658 - BRAVO PISCOYA MARIA GRIMALDINA</t>
+          <t>C001696221 - VENTURA SUCLUPE MARIA FILOMENA</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="I183" s="2" t="n">
@@ -17595,7 +17587,7 @@
       </c>
       <c r="K183" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="L183" t="inlineStr">
@@ -17603,16 +17595,24 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M183" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
+      <c r="M183" t="inlineStr"/>
       <c r="N183" t="inlineStr"/>
       <c r="O183" t="inlineStr"/>
-      <c r="P183" t="inlineStr"/>
-      <c r="Q183" t="inlineStr"/>
-      <c r="R183" t="inlineStr"/>
+      <c r="P183" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="Q183" t="inlineStr">
+        <is>
+          <t>Ninguna, entendió correctamente</t>
+        </is>
+      </c>
+      <c r="R183" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
       <c r="S183" t="inlineStr"/>
       <c r="T183" t="inlineStr">
         <is>
@@ -17658,12 +17658,12 @@
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>C004180367</t>
+          <t>C004168885</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>C004180367 - HUAYTAN CAICEDO WALTER ORLANDO</t>
+          <t>C004168885 - OLIVOS DE VIDAURRE ROSA</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
@@ -17689,7 +17689,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M184" t="inlineStr"/>
+      <c r="M184" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
       <c r="N184" t="inlineStr"/>
       <c r="O184" t="inlineStr"/>
       <c r="P184" t="inlineStr">
@@ -17752,12 +17756,12 @@
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>C004166296</t>
+          <t>C004180367</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>C004166296 - BRIONES SUSANIVAR RUDY GIAMPIER</t>
+          <t>C004180367 - HUAYTAN CAICEDO WALTER ORLANDO</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
@@ -17846,12 +17850,12 @@
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>C004168885</t>
+          <t>C004166296</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>C004168885 - OLIVOS DE VIDAURRE ROSA</t>
+          <t>C004166296 - BRIONES SUSANIVAR RUDY GIAMPIER</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
@@ -17877,11 +17881,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M186" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
+      <c r="M186" t="inlineStr"/>
       <c r="N186" t="inlineStr"/>
       <c r="O186" t="inlineStr"/>
       <c r="P186" t="inlineStr">
@@ -18198,7 +18198,7 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>1000009104</t>
+          <t>1000049464</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -18218,12 +18218,12 @@
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>C001740301</t>
+          <t>C001550158</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>C001740301 - GUERRERO PAREDES MERCEDES ISABEL</t>
+          <t>C001550158 - TORRES RODAS JESSICA NOEMI</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
@@ -18254,7 +18254,7 @@
       <c r="O190" t="inlineStr"/>
       <c r="P190" t="inlineStr">
         <is>
-          <t>Muy dispuesto</t>
+          <t>Algo dispuesto</t>
         </is>
       </c>
       <c r="Q190" t="inlineStr">
@@ -18275,12 +18275,12 @@
       </c>
       <c r="U190" t="inlineStr">
         <is>
-          <t>Cliente</t>
+          <t>Nitro</t>
         </is>
       </c>
       <c r="V190" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>SI - Solo tiene pedido por Nitro</t>
         </is>
       </c>
     </row>
@@ -18292,7 +18292,7 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>1000009104</t>
+          <t>1000049464</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -18312,12 +18312,12 @@
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>C001628093</t>
+          <t>C001405878</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>C001628093 - CRUZ MORANTE LUIS</t>
+          <t>C001405878 - FLORES OLIVA HUGO</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
@@ -18406,12 +18406,12 @@
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>C001550158</t>
+          <t>C001173438</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>C001550158 - TORRES RODAS JESSICA NOEMI</t>
+          <t>C001173438 - RIOS HERRERA MARIA ELOISA</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
@@ -18442,7 +18442,7 @@
       <c r="O192" t="inlineStr"/>
       <c r="P192" t="inlineStr">
         <is>
-          <t>Algo dispuesto</t>
+          <t>Muy dispuesto</t>
         </is>
       </c>
       <c r="Q192" t="inlineStr">
@@ -18463,12 +18463,12 @@
       </c>
       <c r="U192" t="inlineStr">
         <is>
-          <t>Nitro</t>
+          <t>Cliente</t>
         </is>
       </c>
       <c r="V192" t="inlineStr">
         <is>
-          <t>SI - Solo tiene pedido por Nitro</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -18480,7 +18480,7 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>1000049464</t>
+          <t>1000009104</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -18500,12 +18500,12 @@
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>C001405878</t>
+          <t>C001628093</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>C001405878 - FLORES OLIVA HUGO</t>
+          <t>C001628093 - CRUZ MORANTE LUIS</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
@@ -18574,7 +18574,7 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>1000049464</t>
+          <t>1000009104</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -18594,12 +18594,12 @@
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>C001173438</t>
+          <t>C001740301</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>C001173438 - RIOS HERRERA MARIA ELOISA</t>
+          <t>C001740301 - GUERRERO PAREDES MERCEDES ISABEL</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
@@ -18688,12 +18688,12 @@
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>C001082733</t>
+          <t>C001224721</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>C001082733 - DAVILA RUIZ RAMIRO</t>
+          <t>C001224721 - ROJAS PRAVIA MARIA MERCEDES</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
@@ -18745,12 +18745,12 @@
       </c>
       <c r="U195" t="inlineStr">
         <is>
-          <t>Nitro</t>
+          <t>Cliente</t>
         </is>
       </c>
       <c r="V195" t="inlineStr">
         <is>
-          <t>SI - Solo tiene pedido por Nitro</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -18782,12 +18782,12 @@
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>C001521360</t>
+          <t>C001274655</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>C001521360 - CARLOS DE LA CRUZ SERGIO</t>
+          <t>C001274655 - MARTINEZ SOPLAPUCO PEDRO</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
@@ -18813,7 +18813,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M196" t="inlineStr"/>
+      <c r="M196" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
       <c r="N196" t="inlineStr"/>
       <c r="O196" t="inlineStr"/>
       <c r="P196" t="inlineStr">
@@ -18876,12 +18880,12 @@
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>C001553531</t>
+          <t>C001301555</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>C001553531 - RIVAS ARRIAGA JOSE RICARDO</t>
+          <t>C001301555 - AGURTO SANTOS JESSICA</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
@@ -18960,7 +18964,7 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>No tiene tiempo para capacitarse</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
@@ -18970,17 +18974,17 @@
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>C001669258</t>
+          <t>C001082733</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>C001669258 - HUAMAN CARLOS JENY AMELIA</t>
+          <t>C001082733 - DAVILA RUIZ RAMIRO</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="I198" s="2" t="n">
@@ -18993,7 +18997,7 @@
       </c>
       <c r="K198" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="L198" t="inlineStr">
@@ -19004,19 +19008,35 @@
       <c r="M198" t="inlineStr"/>
       <c r="N198" t="inlineStr"/>
       <c r="O198" t="inlineStr"/>
-      <c r="P198" t="inlineStr"/>
-      <c r="Q198" t="inlineStr"/>
-      <c r="R198" t="inlineStr"/>
+      <c r="P198" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="Q198" t="inlineStr">
+        <is>
+          <t>Ninguna, entendió correctamente</t>
+        </is>
+      </c>
+      <c r="R198" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
       <c r="S198" t="inlineStr"/>
       <c r="T198" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U198" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U198" t="inlineStr">
+        <is>
+          <t>Nitro</t>
+        </is>
+      </c>
       <c r="V198" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Solo tiene pedido por Nitro</t>
         </is>
       </c>
     </row>
@@ -19132,7 +19152,7 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>No tiene tiempo para capacitarse</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
@@ -19142,17 +19162,17 @@
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>C001224721</t>
+          <t>C001669258</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>C001224721 - ROJAS PRAVIA MARIA MERCEDES</t>
+          <t>C001669258 - HUAMAN CARLOS JENY AMELIA</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="I200" s="2" t="n">
@@ -19165,7 +19185,7 @@
       </c>
       <c r="K200" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="L200" t="inlineStr">
@@ -19176,35 +19196,19 @@
       <c r="M200" t="inlineStr"/>
       <c r="N200" t="inlineStr"/>
       <c r="O200" t="inlineStr"/>
-      <c r="P200" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="Q200" t="inlineStr">
-        <is>
-          <t>Ninguna, entendió correctamente</t>
-        </is>
-      </c>
-      <c r="R200" t="inlineStr">
-        <is>
-          <t>Mejores promociones</t>
-        </is>
-      </c>
+      <c r="P200" t="inlineStr"/>
+      <c r="Q200" t="inlineStr"/>
+      <c r="R200" t="inlineStr"/>
       <c r="S200" t="inlineStr"/>
       <c r="T200" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U200" t="inlineStr">
-        <is>
-          <t>Cliente</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U200" t="inlineStr"/>
       <c r="V200" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>NO - No hizo pedido</t>
         </is>
       </c>
     </row>
@@ -19236,12 +19240,12 @@
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>C001274655</t>
+          <t>C001521360</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>C001274655 - MARTINEZ SOPLAPUCO PEDRO</t>
+          <t>C001521360 - CARLOS DE LA CRUZ SERGIO</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
@@ -19267,11 +19271,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M201" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
+      <c r="M201" t="inlineStr"/>
       <c r="N201" t="inlineStr"/>
       <c r="O201" t="inlineStr"/>
       <c r="P201" t="inlineStr">
@@ -19334,12 +19334,12 @@
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>C001301555</t>
+          <t>C001553531</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>C001301555 - AGURTO SANTOS JESSICA</t>
+          <t>C001553531 - RIVAS ARRIAGA JOSE RICARDO</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
@@ -20042,7 +20042,7 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>1000009104</t>
+          <t>1000049464</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
@@ -20062,12 +20062,12 @@
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>C004243081</t>
+          <t>C004160232</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>C004243081 - ZENA ACOSTA JOSE LUIS</t>
+          <t>C004160232 - MOLOCHO LOZADA ERLA</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
@@ -20098,7 +20098,7 @@
       <c r="O210" t="inlineStr"/>
       <c r="P210" t="inlineStr">
         <is>
-          <t>Muy dispuesto</t>
+          <t>Algo dispuesto</t>
         </is>
       </c>
       <c r="Q210" t="inlineStr">
@@ -20146,7 +20146,7 @@
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>No tiene tiempo para capacitarse</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E211" t="inlineStr">
@@ -20156,17 +20156,17 @@
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>C004236271</t>
+          <t>C004160837</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>C004236271 - AZULA PEREZ IRMA</t>
+          <t>C004160837 - UTIA TUANAMA KELI</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="I211" s="2" t="n">
@@ -20179,7 +20179,7 @@
       </c>
       <c r="K211" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="L211" t="inlineStr">
@@ -20187,12 +20187,28 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M211" t="inlineStr"/>
+      <c r="M211" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
       <c r="N211" t="inlineStr"/>
       <c r="O211" t="inlineStr"/>
-      <c r="P211" t="inlineStr"/>
-      <c r="Q211" t="inlineStr"/>
-      <c r="R211" t="inlineStr"/>
+      <c r="P211" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="Q211" t="inlineStr">
+        <is>
+          <t>Ninguna, entendió correctamente</t>
+        </is>
+      </c>
+      <c r="R211" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
       <c r="S211" t="inlineStr"/>
       <c r="T211" t="inlineStr">
         <is>
@@ -20318,7 +20334,7 @@
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>No tiene tiempo para capacitarse</t>
         </is>
       </c>
       <c r="E213" t="inlineStr">
@@ -20328,17 +20344,17 @@
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>C004160232</t>
+          <t>C004236271</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>C004160232 - MOLOCHO LOZADA ERLA</t>
+          <t>C004236271 - AZULA PEREZ IRMA</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="I213" s="2" t="n">
@@ -20351,7 +20367,7 @@
       </c>
       <c r="K213" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="L213" t="inlineStr">
@@ -20362,21 +20378,9 @@
       <c r="M213" t="inlineStr"/>
       <c r="N213" t="inlineStr"/>
       <c r="O213" t="inlineStr"/>
-      <c r="P213" t="inlineStr">
-        <is>
-          <t>Algo dispuesto</t>
-        </is>
-      </c>
-      <c r="Q213" t="inlineStr">
-        <is>
-          <t>Ninguna, entendió correctamente</t>
-        </is>
-      </c>
-      <c r="R213" t="inlineStr">
-        <is>
-          <t>Mejores promociones</t>
-        </is>
-      </c>
+      <c r="P213" t="inlineStr"/>
+      <c r="Q213" t="inlineStr"/>
+      <c r="R213" t="inlineStr"/>
       <c r="S213" t="inlineStr"/>
       <c r="T213" t="inlineStr">
         <is>
@@ -20402,7 +20406,7 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>1000049464</t>
+          <t>1000009104</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
@@ -20422,12 +20426,12 @@
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>C004160837</t>
+          <t>C004243081</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>C004160837 - UTIA TUANAMA KELI</t>
+          <t>C004243081 - ZENA ACOSTA JOSE LUIS</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
@@ -20453,11 +20457,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M214" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
+      <c r="M214" t="inlineStr"/>
       <c r="N214" t="inlineStr"/>
       <c r="O214" t="inlineStr"/>
       <c r="P214" t="inlineStr">
@@ -20520,12 +20520,12 @@
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>C001286844</t>
+          <t>C001523972</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>C001286844 - MORA DE LA CRUZ ADELAIDA</t>
+          <t>C001523972 - OFERTAS Y NOVEDADES EL AS S.R.L.</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
@@ -20551,11 +20551,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M215" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
+      <c r="M215" t="inlineStr"/>
       <c r="N215" t="inlineStr"/>
       <c r="O215" t="inlineStr"/>
       <c r="P215" t="inlineStr"/>
@@ -20596,7 +20592,7 @@
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>No tiene tiempo para capacitarse</t>
         </is>
       </c>
       <c r="E216" t="inlineStr">
@@ -20606,17 +20602,17 @@
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>C001216357</t>
+          <t>C001519480</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>C001216357 - CRUZ MEZA NELLY AIDEE</t>
+          <t>C001519480 - RODAS SUAREZ WILMER</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="I216" s="2" t="n">
@@ -20629,7 +20625,7 @@
       </c>
       <c r="K216" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="L216" t="inlineStr">
@@ -20640,21 +20636,9 @@
       <c r="M216" t="inlineStr"/>
       <c r="N216" t="inlineStr"/>
       <c r="O216" t="inlineStr"/>
-      <c r="P216" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="Q216" t="inlineStr">
-        <is>
-          <t>Ninguna, entendió correctamente</t>
-        </is>
-      </c>
-      <c r="R216" t="inlineStr">
-        <is>
-          <t>Mejores promociones</t>
-        </is>
-      </c>
+      <c r="P216" t="inlineStr"/>
+      <c r="Q216" t="inlineStr"/>
+      <c r="R216" t="inlineStr"/>
       <c r="S216" t="inlineStr"/>
       <c r="T216" t="inlineStr">
         <is>
@@ -20663,12 +20647,12 @@
       </c>
       <c r="U216" t="inlineStr">
         <is>
-          <t>Cliente</t>
+          <t>Nitro</t>
         </is>
       </c>
       <c r="V216" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>SI - Solo tiene pedido por Nitro</t>
         </is>
       </c>
     </row>
@@ -20690,7 +20674,7 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>No tiene tiempo para capacitarse</t>
         </is>
       </c>
       <c r="E217" t="inlineStr">
@@ -20700,17 +20684,17 @@
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>C001088415</t>
+          <t>C001286844</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>C001088415 - JUAREZ VELASCO ROSA MARIA</t>
+          <t>C001286844 - MORA DE LA CRUZ ADELAIDA</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="I217" s="2" t="n">
@@ -20723,7 +20707,7 @@
       </c>
       <c r="K217" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="L217" t="inlineStr">
@@ -20731,24 +20715,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M217" t="inlineStr"/>
+      <c r="M217" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
       <c r="N217" t="inlineStr"/>
       <c r="O217" t="inlineStr"/>
-      <c r="P217" t="inlineStr">
-        <is>
-          <t>Algo dispuesto</t>
-        </is>
-      </c>
-      <c r="Q217" t="inlineStr">
-        <is>
-          <t>Ninguna, entendió correctamente</t>
-        </is>
-      </c>
-      <c r="R217" t="inlineStr">
-        <is>
-          <t>Mejores promociones</t>
-        </is>
-      </c>
+      <c r="P217" t="inlineStr"/>
+      <c r="Q217" t="inlineStr"/>
+      <c r="R217" t="inlineStr"/>
       <c r="S217" t="inlineStr"/>
       <c r="T217" t="inlineStr">
         <is>
@@ -20774,7 +20750,7 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>1000009104</t>
+          <t>1000049464</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
@@ -20784,7 +20760,7 @@
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>No tiene tiempo para capacitarse</t>
         </is>
       </c>
       <c r="E218" t="inlineStr">
@@ -20794,17 +20770,17 @@
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>C001079729</t>
+          <t>C001079831</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>C001079729 - DUEÑAS DIAZ ROBERTO</t>
+          <t>C001079831 - LLONTO CAJUSOL MARIA LINDAURA</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="I218" s="2" t="n">
@@ -20817,7 +20793,7 @@
       </c>
       <c r="K218" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="L218" t="inlineStr">
@@ -20828,21 +20804,9 @@
       <c r="M218" t="inlineStr"/>
       <c r="N218" t="inlineStr"/>
       <c r="O218" t="inlineStr"/>
-      <c r="P218" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="Q218" t="inlineStr">
-        <is>
-          <t>Ninguna, entendió correctamente</t>
-        </is>
-      </c>
-      <c r="R218" t="inlineStr">
-        <is>
-          <t>Mejores promociones</t>
-        </is>
-      </c>
+      <c r="P218" t="inlineStr"/>
+      <c r="Q218" t="inlineStr"/>
+      <c r="R218" t="inlineStr"/>
       <c r="S218" t="inlineStr"/>
       <c r="T218" t="inlineStr">
         <is>
@@ -20868,7 +20832,7 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>1000049464</t>
+          <t>1000009104</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
@@ -20878,7 +20842,7 @@
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>No tiene tiempo para capacitarse</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E219" t="inlineStr">
@@ -20888,17 +20852,17 @@
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>C001079831</t>
+          <t>C001079729</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>C001079831 - LLONTO CAJUSOL MARIA LINDAURA</t>
+          <t>C001079729 - DUEÑAS DIAZ ROBERTO</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="I219" s="2" t="n">
@@ -20911,7 +20875,7 @@
       </c>
       <c r="K219" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="L219" t="inlineStr">
@@ -20922,9 +20886,21 @@
       <c r="M219" t="inlineStr"/>
       <c r="N219" t="inlineStr"/>
       <c r="O219" t="inlineStr"/>
-      <c r="P219" t="inlineStr"/>
-      <c r="Q219" t="inlineStr"/>
-      <c r="R219" t="inlineStr"/>
+      <c r="P219" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="Q219" t="inlineStr">
+        <is>
+          <t>Ninguna, entendió correctamente</t>
+        </is>
+      </c>
+      <c r="R219" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
       <c r="S219" t="inlineStr"/>
       <c r="T219" t="inlineStr">
         <is>
@@ -20960,7 +20936,7 @@
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>No tiene tiempo para capacitarse</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E220" t="inlineStr">
@@ -20970,17 +20946,17 @@
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>C001519480</t>
+          <t>C001088415</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>C001519480 - RODAS SUAREZ WILMER</t>
+          <t>C001088415 - JUAREZ VELASCO ROSA MARIA</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="I220" s="2" t="n">
@@ -20993,7 +20969,7 @@
       </c>
       <c r="K220" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="L220" t="inlineStr">
@@ -21004,9 +20980,21 @@
       <c r="M220" t="inlineStr"/>
       <c r="N220" t="inlineStr"/>
       <c r="O220" t="inlineStr"/>
-      <c r="P220" t="inlineStr"/>
-      <c r="Q220" t="inlineStr"/>
-      <c r="R220" t="inlineStr"/>
+      <c r="P220" t="inlineStr">
+        <is>
+          <t>Algo dispuesto</t>
+        </is>
+      </c>
+      <c r="Q220" t="inlineStr">
+        <is>
+          <t>Ninguna, entendió correctamente</t>
+        </is>
+      </c>
+      <c r="R220" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
       <c r="S220" t="inlineStr"/>
       <c r="T220" t="inlineStr">
         <is>
@@ -21015,12 +21003,12 @@
       </c>
       <c r="U220" t="inlineStr">
         <is>
-          <t>Nitro</t>
+          <t>Cliente</t>
         </is>
       </c>
       <c r="V220" t="inlineStr">
         <is>
-          <t>SI - Solo tiene pedido por Nitro</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -21042,7 +21030,7 @@
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>No tiene tiempo para capacitarse</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E221" t="inlineStr">
@@ -21052,17 +21040,17 @@
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>C001523972</t>
+          <t>C001216357</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>C001523972 - OFERTAS Y NOVEDADES EL AS S.R.L.</t>
+          <t>C001216357 - CRUZ MEZA NELLY AIDEE</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="I221" s="2" t="n">
@@ -21075,7 +21063,7 @@
       </c>
       <c r="K221" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="L221" t="inlineStr">
@@ -21086,9 +21074,21 @@
       <c r="M221" t="inlineStr"/>
       <c r="N221" t="inlineStr"/>
       <c r="O221" t="inlineStr"/>
-      <c r="P221" t="inlineStr"/>
-      <c r="Q221" t="inlineStr"/>
-      <c r="R221" t="inlineStr"/>
+      <c r="P221" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="Q221" t="inlineStr">
+        <is>
+          <t>Ninguna, entendió correctamente</t>
+        </is>
+      </c>
+      <c r="R221" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
       <c r="S221" t="inlineStr"/>
       <c r="T221" t="inlineStr">
         <is>
@@ -21208,7 +21208,7 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>1000049464</t>
+          <t>1000009104</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
@@ -21228,12 +21228,12 @@
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>C001570988</t>
+          <t>C004218405</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>C001570988 - CASTRO PISCOYA WILLIAN YOVANI</t>
+          <t>C004218405 - SUCLUPE LOPEZ WILLIAN ALBERTO</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
@@ -21259,7 +21259,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M223" t="inlineStr"/>
+      <c r="M223" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
       <c r="N223" t="inlineStr"/>
       <c r="O223" t="inlineStr"/>
       <c r="P223" t="inlineStr">
@@ -21269,7 +21273,7 @@
       </c>
       <c r="Q223" t="inlineStr">
         <is>
-          <t>Iniciar sesión</t>
+          <t>Ninguna, entendió correctamente</t>
         </is>
       </c>
       <c r="R223" t="inlineStr">
@@ -21312,7 +21316,7 @@
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>No tiene tiempo para capacitarse</t>
         </is>
       </c>
       <c r="E224" t="inlineStr">
@@ -21322,17 +21326,17 @@
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>C001723751</t>
+          <t>C004048977</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>C001723751 - PAREDES DE ESPINOZA MARIA DEL ELMA</t>
+          <t>C004048977 - PURIHUAMAN MANAYAY CECILIA</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="I224" s="2" t="n">
@@ -21345,7 +21349,7 @@
       </c>
       <c r="K224" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="L224" t="inlineStr">
@@ -21353,24 +21357,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M224" t="inlineStr"/>
+      <c r="M224" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
       <c r="N224" t="inlineStr"/>
       <c r="O224" t="inlineStr"/>
-      <c r="P224" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="Q224" t="inlineStr">
-        <is>
-          <t>Ninguna, entendió correctamente</t>
-        </is>
-      </c>
-      <c r="R224" t="inlineStr">
-        <is>
-          <t>Mejores promociones</t>
-        </is>
-      </c>
+      <c r="P224" t="inlineStr"/>
+      <c r="Q224" t="inlineStr"/>
+      <c r="R224" t="inlineStr"/>
       <c r="S224" t="inlineStr"/>
       <c r="T224" t="inlineStr">
         <is>
@@ -21396,7 +21392,7 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>1000009104</t>
+          <t>1000049464</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
@@ -21416,12 +21412,12 @@
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>C001767390</t>
+          <t>C004097806</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>C001767390 - SANDOVAL SANDOVAL DIANA CAROLINA</t>
+          <t>C004097806 - HERNANDEZ FLORES WILDOR</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
@@ -21457,7 +21453,7 @@
       </c>
       <c r="Q225" t="inlineStr">
         <is>
-          <t>Iniciar sesión</t>
+          <t>Ninguna, entendió correctamente</t>
         </is>
       </c>
       <c r="R225" t="inlineStr">
@@ -21486,7 +21482,7 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>1000009104</t>
+          <t>1000049464</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
@@ -21506,12 +21502,12 @@
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>C004218405</t>
+          <t>C001570988</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>C004218405 - SUCLUPE LOPEZ WILLIAN ALBERTO</t>
+          <t>C001570988 - CASTRO PISCOYA WILLIAN YOVANI</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
@@ -21537,11 +21533,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M226" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
+      <c r="M226" t="inlineStr"/>
       <c r="N226" t="inlineStr"/>
       <c r="O226" t="inlineStr"/>
       <c r="P226" t="inlineStr">
@@ -21551,7 +21543,7 @@
       </c>
       <c r="Q226" t="inlineStr">
         <is>
-          <t>Ninguna, entendió correctamente</t>
+          <t>Iniciar sesión</t>
         </is>
       </c>
       <c r="R226" t="inlineStr">
@@ -21584,7 +21576,7 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>1000049464</t>
+          <t>1000009104</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
@@ -21604,12 +21596,12 @@
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>C004097806</t>
+          <t>C001767390</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>C004097806 - HERNANDEZ FLORES WILDOR</t>
+          <t>C001767390 - SANDOVAL SANDOVAL DIANA CAROLINA</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
@@ -21645,7 +21637,7 @@
       </c>
       <c r="Q227" t="inlineStr">
         <is>
-          <t>Ninguna, entendió correctamente</t>
+          <t>Iniciar sesión</t>
         </is>
       </c>
       <c r="R227" t="inlineStr">
@@ -21674,7 +21666,7 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>1000049464</t>
+          <t>1000009104</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
@@ -21684,7 +21676,7 @@
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>No tiene tiempo para capacitarse</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E228" t="inlineStr">
@@ -21694,17 +21686,17 @@
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>C004048977</t>
+          <t>C001718760</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>C004048977 - PURIHUAMAN MANAYAY CECILIA</t>
+          <t>C001718760 - GUEVARA MONJE CELINDA IRENE</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="I228" s="2" t="n">
@@ -21717,7 +21709,7 @@
       </c>
       <c r="K228" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="L228" t="inlineStr">
@@ -21727,14 +21719,26 @@
       </c>
       <c r="M228" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="N228" t="inlineStr"/>
       <c r="O228" t="inlineStr"/>
-      <c r="P228" t="inlineStr"/>
-      <c r="Q228" t="inlineStr"/>
-      <c r="R228" t="inlineStr"/>
+      <c r="P228" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="Q228" t="inlineStr">
+        <is>
+          <t>Ninguna, entendió correctamente</t>
+        </is>
+      </c>
+      <c r="R228" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
       <c r="S228" t="inlineStr"/>
       <c r="T228" t="inlineStr">
         <is>
@@ -21770,7 +21774,7 @@
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>Prefiere pedir con su vendedor</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E229" t="inlineStr">
@@ -21780,17 +21784,17 @@
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>C004164415</t>
+          <t>C001723751</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>C004164415 - MANAYAY DE LOS SANTOS GERMAN OSCAR</t>
+          <t>C001723751 - PAREDES DE ESPINOZA MARIA DEL ELMA</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="I229" s="2" t="n">
@@ -21803,7 +21807,7 @@
       </c>
       <c r="K229" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="L229" t="inlineStr">
@@ -21814,9 +21818,21 @@
       <c r="M229" t="inlineStr"/>
       <c r="N229" t="inlineStr"/>
       <c r="O229" t="inlineStr"/>
-      <c r="P229" t="inlineStr"/>
-      <c r="Q229" t="inlineStr"/>
-      <c r="R229" t="inlineStr"/>
+      <c r="P229" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="Q229" t="inlineStr">
+        <is>
+          <t>Ninguna, entendió correctamente</t>
+        </is>
+      </c>
+      <c r="R229" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
       <c r="S229" t="inlineStr"/>
       <c r="T229" t="inlineStr">
         <is>
@@ -21862,12 +21878,12 @@
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>C004159325</t>
+          <t>C001733149</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>C004159325 - CASIANO BAUTISTA JAZMIN DEL MILAGRO</t>
+          <t>C001733149 - HUAMAN EXEBIO BERTHA ROSA</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
@@ -21893,7 +21909,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M230" t="inlineStr"/>
+      <c r="M230" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
       <c r="N230" t="inlineStr"/>
       <c r="O230" t="inlineStr"/>
       <c r="P230" t="inlineStr">
@@ -21942,7 +21962,7 @@
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>No tiene tiempo para capacitarse</t>
         </is>
       </c>
       <c r="E231" t="inlineStr">
@@ -21952,17 +21972,17 @@
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>C001733149</t>
+          <t>C001735365</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>C001733149 - HUAMAN EXEBIO BERTHA ROSA</t>
+          <t>C001735365 - PUMA GALVEZ VERONICA</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="I231" s="2" t="n">
@@ -21975,7 +21995,7 @@
       </c>
       <c r="K231" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="L231" t="inlineStr">
@@ -21983,28 +22003,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M231" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
+      <c r="M231" t="inlineStr"/>
       <c r="N231" t="inlineStr"/>
       <c r="O231" t="inlineStr"/>
-      <c r="P231" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="Q231" t="inlineStr">
-        <is>
-          <t>Ninguna, entendió correctamente</t>
-        </is>
-      </c>
-      <c r="R231" t="inlineStr">
-        <is>
-          <t>Mejores promociones</t>
-        </is>
-      </c>
+      <c r="P231" t="inlineStr"/>
+      <c r="Q231" t="inlineStr"/>
+      <c r="R231" t="inlineStr"/>
       <c r="S231" t="inlineStr"/>
       <c r="T231" t="inlineStr">
         <is>
@@ -22036,7 +22040,7 @@
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>No tiene tiempo para capacitarse</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E232" t="inlineStr">
@@ -22046,17 +22050,17 @@
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>C001735365</t>
+          <t>C001691302</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>C001735365 - PUMA GALVEZ VERONICA</t>
+          <t>C001691302 - BERNILLA GARCIA ESTHER JHONA</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="I232" s="2" t="n">
@@ -22069,7 +22073,7 @@
       </c>
       <c r="K232" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="L232" t="inlineStr">
@@ -22080,19 +22084,35 @@
       <c r="M232" t="inlineStr"/>
       <c r="N232" t="inlineStr"/>
       <c r="O232" t="inlineStr"/>
-      <c r="P232" t="inlineStr"/>
-      <c r="Q232" t="inlineStr"/>
-      <c r="R232" t="inlineStr"/>
+      <c r="P232" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="Q232" t="inlineStr">
+        <is>
+          <t>Ninguna, entendió correctamente</t>
+        </is>
+      </c>
+      <c r="R232" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
       <c r="S232" t="inlineStr"/>
       <c r="T232" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U232" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U232" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
       <c r="V232" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -22104,7 +22124,7 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>1000009104</t>
+          <t>1000049464</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
@@ -22124,12 +22144,12 @@
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>C001718760</t>
+          <t>C001684104</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>C001718760 - GUEVARA MONJE CELINDA IRENE</t>
+          <t>C001684104 - HUAMAN SOPLAPUCO CECI FLOR</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
@@ -22180,17 +22200,13 @@
       <c r="S233" t="inlineStr"/>
       <c r="T233" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U233" t="inlineStr">
-        <is>
-          <t>Cliente</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U233" t="inlineStr"/>
       <c r="V233" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>NO - No hizo pedido</t>
         </is>
       </c>
     </row>
@@ -22222,12 +22238,12 @@
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>C001684104</t>
+          <t>C004159325</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>C001684104 - HUAMAN SOPLAPUCO CECI FLOR</t>
+          <t>C004159325 - CASIANO BAUTISTA JAZMIN DEL MILAGRO</t>
         </is>
       </c>
       <c r="H234" t="inlineStr">
@@ -22253,11 +22269,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M234" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
+      <c r="M234" t="inlineStr"/>
       <c r="N234" t="inlineStr"/>
       <c r="O234" t="inlineStr"/>
       <c r="P234" t="inlineStr">
@@ -22306,7 +22318,7 @@
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Prefiere pedir con su vendedor</t>
         </is>
       </c>
       <c r="E235" t="inlineStr">
@@ -22316,17 +22328,17 @@
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>C001691302</t>
+          <t>C004164415</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>C001691302 - BERNILLA GARCIA ESTHER JHONA</t>
+          <t>C004164415 - MANAYAY DE LOS SANTOS GERMAN OSCAR</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="I235" s="2" t="n">
@@ -22339,7 +22351,7 @@
       </c>
       <c r="K235" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="L235" t="inlineStr">
@@ -22350,21 +22362,9 @@
       <c r="M235" t="inlineStr"/>
       <c r="N235" t="inlineStr"/>
       <c r="O235" t="inlineStr"/>
-      <c r="P235" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="Q235" t="inlineStr">
-        <is>
-          <t>Ninguna, entendió correctamente</t>
-        </is>
-      </c>
-      <c r="R235" t="inlineStr">
-        <is>
-          <t>Mejores promociones</t>
-        </is>
-      </c>
+      <c r="P235" t="inlineStr"/>
+      <c r="Q235" t="inlineStr"/>
+      <c r="R235" t="inlineStr"/>
       <c r="S235" t="inlineStr"/>
       <c r="T235" t="inlineStr">
         <is>
@@ -22390,7 +22390,7 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>1000049464</t>
+          <t>1000009104</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
@@ -22410,12 +22410,12 @@
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>C001545229</t>
+          <t>C001381139</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>C001545229 - VALLEJOS DIAZ MARIA CANDELARIA</t>
+          <t>C001381139 - YLUQUIS DE RIOS LUISA</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
@@ -22446,7 +22446,7 @@
       <c r="O236" t="inlineStr"/>
       <c r="P236" t="inlineStr">
         <is>
-          <t>Nada dispuesto</t>
+          <t>Muy dispuesto</t>
         </is>
       </c>
       <c r="Q236" t="inlineStr">
@@ -22462,17 +22462,13 @@
       <c r="S236" t="inlineStr"/>
       <c r="T236" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U236" t="inlineStr">
-        <is>
-          <t>Cliente</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U236" t="inlineStr"/>
       <c r="V236" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>NO - No hizo pedido</t>
         </is>
       </c>
     </row>
@@ -22494,7 +22490,7 @@
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>No tiene tiempo para capacitarse</t>
         </is>
       </c>
       <c r="E237" t="inlineStr">
@@ -22504,17 +22500,17 @@
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>C001414604</t>
+          <t>C001284564</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>C001414604 - VASQUEZ RAMIREZ YENY CARINA</t>
+          <t>C001284564 - MANAYAY SOTO MARI CRUZ YESIBEL</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="I237" s="2" t="n">
@@ -22527,7 +22523,7 @@
       </c>
       <c r="K237" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="L237" t="inlineStr">
@@ -22535,28 +22531,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M237" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
+      <c r="M237" t="inlineStr"/>
       <c r="N237" t="inlineStr"/>
       <c r="O237" t="inlineStr"/>
-      <c r="P237" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="Q237" t="inlineStr">
-        <is>
-          <t>Ninguna, entendió correctamente</t>
-        </is>
-      </c>
-      <c r="R237" t="inlineStr">
-        <is>
-          <t>Mejores promociones</t>
-        </is>
-      </c>
+      <c r="P237" t="inlineStr"/>
+      <c r="Q237" t="inlineStr"/>
+      <c r="R237" t="inlineStr"/>
       <c r="S237" t="inlineStr"/>
       <c r="T237" t="inlineStr">
         <is>
@@ -22602,12 +22582,12 @@
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>C001516332</t>
+          <t>C001475804</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>C001516332 - CARMONA ROJAS MAGALI LUCILA</t>
+          <t>C001475804 - PISFIL SIMPALO PETRONILA MARGARITA</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
@@ -22633,11 +22613,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M238" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
+      <c r="M238" t="inlineStr"/>
       <c r="N238" t="inlineStr"/>
       <c r="O238" t="inlineStr"/>
       <c r="P238" t="inlineStr"/>
@@ -22651,12 +22627,12 @@
       </c>
       <c r="U238" t="inlineStr">
         <is>
-          <t>Cliente</t>
+          <t>Nitro</t>
         </is>
       </c>
       <c r="V238" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>SI - Solo tiene pedido por Nitro</t>
         </is>
       </c>
     </row>
@@ -22688,12 +22664,12 @@
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>C001487761</t>
+          <t>C001414604</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>C001487761 - TORRES HEREDIA ENNA ROXANA</t>
+          <t>C001414604 - VASQUEZ RAMIREZ YENY CARINA</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
@@ -22719,7 +22695,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M239" t="inlineStr"/>
+      <c r="M239" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
       <c r="N239" t="inlineStr"/>
       <c r="O239" t="inlineStr"/>
       <c r="P239" t="inlineStr">
@@ -22772,7 +22752,7 @@
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>No tiene tiempo para capacitarse</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E240" t="inlineStr">
@@ -22782,17 +22762,17 @@
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>C001475804</t>
+          <t>C001487761</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>C001475804 - PISFIL SIMPALO PETRONILA MARGARITA</t>
+          <t>C001487761 - TORRES HEREDIA ENNA ROXANA</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="I240" s="2" t="n">
@@ -22805,7 +22785,7 @@
       </c>
       <c r="K240" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="L240" t="inlineStr">
@@ -22816,9 +22796,21 @@
       <c r="M240" t="inlineStr"/>
       <c r="N240" t="inlineStr"/>
       <c r="O240" t="inlineStr"/>
-      <c r="P240" t="inlineStr"/>
-      <c r="Q240" t="inlineStr"/>
-      <c r="R240" t="inlineStr"/>
+      <c r="P240" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="Q240" t="inlineStr">
+        <is>
+          <t>Ninguna, entendió correctamente</t>
+        </is>
+      </c>
+      <c r="R240" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
       <c r="S240" t="inlineStr"/>
       <c r="T240" t="inlineStr">
         <is>
@@ -22827,12 +22819,12 @@
       </c>
       <c r="U240" t="inlineStr">
         <is>
-          <t>Nitro</t>
+          <t>Cliente</t>
         </is>
       </c>
       <c r="V240" t="inlineStr">
         <is>
-          <t>SI - Solo tiene pedido por Nitro</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -22844,7 +22836,7 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>1000009104</t>
+          <t>1000049464</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
@@ -22854,7 +22846,7 @@
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>No tiene tiempo para capacitarse</t>
         </is>
       </c>
       <c r="E241" t="inlineStr">
@@ -22864,17 +22856,17 @@
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>C001381139</t>
+          <t>C001516332</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>C001381139 - YLUQUIS DE RIOS LUISA</t>
+          <t>C001516332 - CARMONA ROJAS MAGALI LUCILA</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="I241" s="2" t="n">
@@ -22887,7 +22879,7 @@
       </c>
       <c r="K241" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="L241" t="inlineStr">
@@ -22895,34 +22887,30 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M241" t="inlineStr"/>
+      <c r="M241" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
       <c r="N241" t="inlineStr"/>
       <c r="O241" t="inlineStr"/>
-      <c r="P241" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="Q241" t="inlineStr">
-        <is>
-          <t>Ninguna, entendió correctamente</t>
-        </is>
-      </c>
-      <c r="R241" t="inlineStr">
-        <is>
-          <t>Mejores promociones</t>
-        </is>
-      </c>
+      <c r="P241" t="inlineStr"/>
+      <c r="Q241" t="inlineStr"/>
+      <c r="R241" t="inlineStr"/>
       <c r="S241" t="inlineStr"/>
       <c r="T241" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U241" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U241" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
       <c r="V241" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -22944,7 +22932,7 @@
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>No tiene tiempo para capacitarse</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E242" t="inlineStr">
@@ -22954,17 +22942,17 @@
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>C001284564</t>
+          <t>C001545229</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>C001284564 - MANAYAY SOTO MARI CRUZ YESIBEL</t>
+          <t>C001545229 - VALLEJOS DIAZ MARIA CANDELARIA</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="I242" s="2" t="n">
@@ -22977,7 +22965,7 @@
       </c>
       <c r="K242" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="L242" t="inlineStr">
@@ -22988,9 +22976,21 @@
       <c r="M242" t="inlineStr"/>
       <c r="N242" t="inlineStr"/>
       <c r="O242" t="inlineStr"/>
-      <c r="P242" t="inlineStr"/>
-      <c r="Q242" t="inlineStr"/>
-      <c r="R242" t="inlineStr"/>
+      <c r="P242" t="inlineStr">
+        <is>
+          <t>Nada dispuesto</t>
+        </is>
+      </c>
+      <c r="Q242" t="inlineStr">
+        <is>
+          <t>Ninguna, entendió correctamente</t>
+        </is>
+      </c>
+      <c r="R242" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
       <c r="S242" t="inlineStr"/>
       <c r="T242" t="inlineStr">
         <is>
